--- a/collinsville.xlsx
+++ b/collinsville.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9E4DDAE-73F7-48F0-AF4B-ABA13121B2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C20AD3E3-DB4F-4DE3-80FD-58097933E49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-10910" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carrier Route Scheme" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4676" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4684" uniqueCount="689">
   <si>
     <t>Scheme Listing by CRID for ZIP Code 74021</t>
   </si>
@@ -335,153 +335,153 @@
     <t>R003</t>
   </si>
   <si>
+    <t>13600</t>
+  </si>
+  <si>
+    <t>14999</t>
+  </si>
+  <si>
+    <t>58TH EAST</t>
+  </si>
+  <si>
+    <t>13300</t>
+  </si>
+  <si>
+    <t>14199</t>
+  </si>
+  <si>
+    <t>59TH EAST</t>
+  </si>
+  <si>
+    <t>14700</t>
+  </si>
+  <si>
+    <t>60TH EAST</t>
+  </si>
+  <si>
+    <t>14200</t>
+  </si>
+  <si>
+    <t>14299</t>
+  </si>
+  <si>
+    <t>61ST EAST</t>
+  </si>
+  <si>
+    <t>14100</t>
+  </si>
+  <si>
+    <t>62ND EAST</t>
+  </si>
+  <si>
+    <t>63RD EAST</t>
+  </si>
+  <si>
+    <t>14398</t>
+  </si>
+  <si>
+    <t>64TH EAST</t>
+  </si>
+  <si>
+    <t>14400</t>
+  </si>
+  <si>
+    <t>14499</t>
+  </si>
+  <si>
+    <t>66TH EAST</t>
+  </si>
+  <si>
+    <t>16800</t>
+  </si>
+  <si>
+    <t>17199</t>
+  </si>
+  <si>
+    <t>67TH EAST</t>
+  </si>
+  <si>
+    <t>68TH EAST</t>
+  </si>
+  <si>
+    <t>69TH EAST</t>
+  </si>
+  <si>
+    <t>12100</t>
+  </si>
+  <si>
+    <t>13699</t>
+  </si>
+  <si>
+    <t>70TH EAST</t>
+  </si>
+  <si>
+    <t>14099</t>
+  </si>
+  <si>
+    <t>71ST EAST</t>
+  </si>
+  <si>
+    <t>72ND EAST</t>
+  </si>
+  <si>
+    <t>12899</t>
+  </si>
+  <si>
+    <t>73RD EAST</t>
+  </si>
+  <si>
+    <t>74TH EAST</t>
+  </si>
+  <si>
+    <t>12799</t>
+  </si>
+  <si>
+    <t>75TH EAST</t>
+  </si>
+  <si>
+    <t>14500</t>
+  </si>
+  <si>
+    <t>14899</t>
+  </si>
+  <si>
+    <t>76TH EAST</t>
+  </si>
+  <si>
+    <t>13100</t>
+  </si>
+  <si>
+    <t>13499</t>
+  </si>
+  <si>
+    <t>77TH EAST</t>
+  </si>
+  <si>
+    <t>14600</t>
+  </si>
+  <si>
+    <t>14799</t>
+  </si>
+  <si>
+    <t>12700</t>
+  </si>
+  <si>
+    <t>83RD EAST</t>
+  </si>
+  <si>
+    <t>15401</t>
+  </si>
+  <si>
+    <t>15499</t>
+  </si>
+  <si>
+    <t>85TH EAST</t>
+  </si>
+  <si>
     <t>13700</t>
   </si>
   <si>
-    <t>14999</t>
-  </si>
-  <si>
-    <t>58TH EAST</t>
-  </si>
-  <si>
-    <t>13300</t>
-  </si>
-  <si>
-    <t>13600</t>
-  </si>
-  <si>
-    <t>14199</t>
-  </si>
-  <si>
-    <t>59TH EAST</t>
-  </si>
-  <si>
-    <t>14700</t>
-  </si>
-  <si>
-    <t>60TH EAST</t>
-  </si>
-  <si>
-    <t>14200</t>
-  </si>
-  <si>
-    <t>14299</t>
-  </si>
-  <si>
-    <t>61ST EAST</t>
-  </si>
-  <si>
-    <t>14100</t>
-  </si>
-  <si>
-    <t>62ND EAST</t>
-  </si>
-  <si>
-    <t>63RD EAST</t>
-  </si>
-  <si>
-    <t>14398</t>
-  </si>
-  <si>
-    <t>64TH EAST</t>
-  </si>
-  <si>
-    <t>14400</t>
-  </si>
-  <si>
-    <t>14499</t>
-  </si>
-  <si>
-    <t>66TH EAST</t>
-  </si>
-  <si>
-    <t>16800</t>
-  </si>
-  <si>
-    <t>17199</t>
-  </si>
-  <si>
-    <t>67TH EAST</t>
-  </si>
-  <si>
-    <t>68TH EAST</t>
-  </si>
-  <si>
-    <t>69TH EAST</t>
-  </si>
-  <si>
-    <t>12100</t>
-  </si>
-  <si>
-    <t>13699</t>
-  </si>
-  <si>
-    <t>70TH EAST</t>
-  </si>
-  <si>
-    <t>14099</t>
-  </si>
-  <si>
-    <t>71ST EAST</t>
-  </si>
-  <si>
-    <t>72ND EAST</t>
-  </si>
-  <si>
-    <t>12899</t>
-  </si>
-  <si>
-    <t>73RD EAST</t>
-  </si>
-  <si>
-    <t>74TH EAST</t>
-  </si>
-  <si>
-    <t>12799</t>
-  </si>
-  <si>
-    <t>75TH EAST</t>
-  </si>
-  <si>
-    <t>14500</t>
-  </si>
-  <si>
-    <t>14899</t>
-  </si>
-  <si>
-    <t>76TH EAST</t>
-  </si>
-  <si>
-    <t>13100</t>
-  </si>
-  <si>
-    <t>13499</t>
-  </si>
-  <si>
-    <t>77TH EAST</t>
-  </si>
-  <si>
-    <t>14600</t>
-  </si>
-  <si>
-    <t>14799</t>
-  </si>
-  <si>
-    <t>12700</t>
-  </si>
-  <si>
-    <t>83RD EAST</t>
-  </si>
-  <si>
-    <t>15401</t>
-  </si>
-  <si>
-    <t>15499</t>
-  </si>
-  <si>
-    <t>85TH EAST</t>
-  </si>
-  <si>
     <t>14298</t>
   </si>
   <si>
@@ -1109,7 +1109,7 @@
     <t>135TH EAST</t>
   </si>
   <si>
-    <t>5900</t>
+    <t>5500</t>
   </si>
   <si>
     <t>136TH</t>
@@ -1232,12 +1232,18 @@
     <t>15301</t>
   </si>
   <si>
+    <t>5600</t>
+  </si>
+  <si>
+    <t>5699</t>
+  </si>
+  <si>
+    <t>140TH</t>
+  </si>
+  <si>
     <t>11499</t>
   </si>
   <si>
-    <t>140TH</t>
-  </si>
-  <si>
     <t>8501</t>
   </si>
   <si>
@@ -1253,9 +1259,6 @@
     <t>141ST</t>
   </si>
   <si>
-    <t>5500</t>
-  </si>
-  <si>
     <t>5799</t>
   </si>
   <si>
@@ -2075,10 +2078,10 @@
     <t>YALE</t>
   </si>
   <si>
-    <t>Total Line items: 583</t>
-  </si>
-  <si>
-    <t>ZIP CODE</t>
+    <t>Total Line items: 584</t>
+  </si>
+  <si>
+    <t>zip code</t>
   </si>
 </sst>
 </file>
@@ -2476,7 +2479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I586"/>
+  <dimension ref="A1:I587"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="8" customWidth="1"/>
@@ -2484,7 +2487,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -2514,7 +2517,7 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>4</v>
@@ -4900,19 +4903,19 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" t="s">
         <v>111</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85" t="s">
-        <v>14</v>
-      </c>
-      <c r="E85" t="s">
-        <v>112</v>
       </c>
       <c r="F85" t="s">
         <v>94</v>
@@ -4941,7 +4944,7 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F86" t="s">
         <v>64</v>
@@ -4958,7 +4961,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>107</v>
@@ -4970,7 +4973,7 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F87" t="s">
         <v>94</v>
@@ -4999,7 +5002,7 @@
         <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F88" t="s">
         <v>64</v>
@@ -5016,19 +5019,19 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" t="s">
         <v>116</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" t="s">
-        <v>14</v>
-      </c>
-      <c r="E89" t="s">
-        <v>117</v>
       </c>
       <c r="F89" t="s">
         <v>94</v>
@@ -5045,7 +5048,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>99</v>
@@ -5057,7 +5060,7 @@
         <v>14</v>
       </c>
       <c r="E90" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F90" t="s">
         <v>94</v>
@@ -5074,7 +5077,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>99</v>
@@ -5086,7 +5089,7 @@
         <v>14</v>
       </c>
       <c r="E91" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F91" t="s">
         <v>94</v>
@@ -5103,19 +5106,19 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" t="s">
         <v>121</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92" t="s">
-        <v>14</v>
-      </c>
-      <c r="E92" t="s">
-        <v>122</v>
       </c>
       <c r="F92" t="s">
         <v>94</v>
@@ -5132,19 +5135,19 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="C93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" t="s">
         <v>124</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" t="s">
-        <v>14</v>
-      </c>
-      <c r="E93" t="s">
-        <v>125</v>
       </c>
       <c r="F93" t="s">
         <v>94</v>
@@ -5161,19 +5164,19 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s">
         <v>127</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" t="s">
-        <v>128</v>
       </c>
       <c r="F94" t="s">
         <v>94</v>
@@ -5190,7 +5193,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>92</v>
@@ -5202,7 +5205,7 @@
         <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F95" t="s">
         <v>94</v>
@@ -5219,10 +5222,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>7</v>
@@ -5231,7 +5234,7 @@
         <v>14</v>
       </c>
       <c r="E96" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F96" t="s">
         <v>94</v>
@@ -5248,19 +5251,19 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" t="s">
         <v>132</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" t="s">
-        <v>133</v>
       </c>
       <c r="F97" t="s">
         <v>94</v>
@@ -5277,10 +5280,10 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>7</v>
@@ -5289,7 +5292,7 @@
         <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F98" t="s">
         <v>94</v>
@@ -5309,16 +5312,16 @@
         <v>96</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" t="s">
         <v>134</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D99" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" t="s">
-        <v>135</v>
       </c>
       <c r="F99" t="s">
         <v>94</v>
@@ -5335,10 +5338,10 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>7</v>
@@ -5347,7 +5350,7 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F100" t="s">
         <v>94</v>
@@ -5364,10 +5367,10 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>7</v>
@@ -5376,7 +5379,7 @@
         <v>14</v>
       </c>
       <c r="E101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F101" t="s">
         <v>94</v>
@@ -5393,19 +5396,19 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s">
         <v>137</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D102" t="s">
-        <v>14</v>
-      </c>
-      <c r="E102" t="s">
-        <v>138</v>
       </c>
       <c r="F102" t="s">
         <v>94</v>
@@ -5422,10 +5425,10 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>7</v>
@@ -5434,7 +5437,7 @@
         <v>14</v>
       </c>
       <c r="E103" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F103" t="s">
         <v>94</v>
@@ -5451,10 +5454,10 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>7</v>
@@ -5463,7 +5466,7 @@
         <v>14</v>
       </c>
       <c r="E104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F104" t="s">
         <v>94</v>
@@ -5480,19 +5483,19 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s">
         <v>140</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D105" t="s">
-        <v>14</v>
-      </c>
-      <c r="E105" t="s">
-        <v>141</v>
       </c>
       <c r="F105" t="s">
         <v>94</v>
@@ -5509,10 +5512,10 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>7</v>
@@ -5521,7 +5524,7 @@
         <v>14</v>
       </c>
       <c r="E106" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F106" t="s">
         <v>94</v>
@@ -5538,11 +5541,11 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>7</v>
       </c>
@@ -5550,7 +5553,7 @@
         <v>14</v>
       </c>
       <c r="E107" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F107" t="s">
         <v>94</v>
@@ -5567,7 +5570,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>92</v>
@@ -5579,7 +5582,7 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F108" t="s">
         <v>94</v>
@@ -5596,19 +5599,19 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="C109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s">
         <v>146</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D109" t="s">
-        <v>14</v>
-      </c>
-      <c r="E109" t="s">
-        <v>147</v>
       </c>
       <c r="F109" t="s">
         <v>94</v>
@@ -5625,11 +5628,11 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>7</v>
       </c>
@@ -5637,7 +5640,7 @@
         <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F110" t="s">
         <v>94</v>
@@ -5654,7 +5657,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>104</v>
@@ -5666,7 +5669,7 @@
         <v>14</v>
       </c>
       <c r="E111" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F111" t="s">
         <v>94</v>
@@ -5683,19 +5686,19 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" t="s">
+        <v>14</v>
+      </c>
+      <c r="E112" t="s">
         <v>153</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D112" t="s">
-        <v>14</v>
-      </c>
-      <c r="E112" t="s">
-        <v>154</v>
       </c>
       <c r="F112" t="s">
         <v>94</v>
@@ -5712,7 +5715,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>155</v>
@@ -5770,10 +5773,10 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>7</v>
@@ -5857,7 +5860,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>166</v>
@@ -5944,7 +5947,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>166</v>
@@ -6089,7 +6092,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>104</v>
@@ -6205,7 +6208,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>186</v>
@@ -6292,10 +6295,10 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>7</v>
@@ -6524,7 +6527,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>204</v>
@@ -6553,7 +6556,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>99</v>
@@ -6611,7 +6614,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>99</v>
@@ -6669,7 +6672,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>207</v>
@@ -6756,7 +6759,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>99</v>
@@ -6814,10 +6817,10 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>7</v>
@@ -6930,7 +6933,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>217</v>
@@ -6959,10 +6962,10 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>7</v>
@@ -7049,7 +7052,7 @@
         <v>206</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>7</v>
@@ -7075,10 +7078,10 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>7</v>
@@ -7336,10 +7339,10 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>7</v>
@@ -7513,7 +7516,7 @@
         <v>248</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>7</v>
@@ -8119,7 +8122,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>277</v>
@@ -8902,7 +8905,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>207</v>
@@ -9050,7 +9053,7 @@
         <v>305</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>7</v>
@@ -9079,7 +9082,7 @@
         <v>109</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>7</v>
@@ -9137,7 +9140,7 @@
         <v>266</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>7</v>
@@ -9398,7 +9401,7 @@
         <v>266</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>7</v>
@@ -9453,7 +9456,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>171</v>
@@ -9717,7 +9720,7 @@
         <v>299</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>7</v>
@@ -9743,10 +9746,10 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>7</v>
@@ -10123,7 +10126,7 @@
         <v>198</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>7</v>
@@ -10149,10 +10152,10 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B266" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>7</v>
@@ -10381,7 +10384,7 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>202</v>
@@ -10410,7 +10413,7 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>340</v>
@@ -10468,10 +10471,10 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B277" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>7</v>
@@ -10558,7 +10561,7 @@
         <v>198</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>7</v>
@@ -10584,7 +10587,7 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" s="3" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>347</v>
@@ -10729,7 +10732,7 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>104</v>
@@ -10758,7 +10761,7 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" s="3" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>202</v>
@@ -10903,7 +10906,7 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>318</v>
@@ -11022,7 +11025,7 @@
         <v>103</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>7</v>
@@ -11077,7 +11080,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>318</v>
@@ -11106,7 +11109,7 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>204</v>
@@ -11164,7 +11167,7 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>332</v>
@@ -11222,7 +11225,7 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>332</v>
@@ -11280,7 +11283,7 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>277</v>
@@ -11338,10 +11341,10 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>7</v>
@@ -11918,7 +11921,7 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" s="3" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>391</v>
@@ -12353,7 +12356,7 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>107</v>
@@ -12440,7 +12443,7 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A345" s="3" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>361</v>
@@ -12614,10 +12617,10 @@
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A351" s="3" t="s">
-        <v>233</v>
+        <v>405</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>7</v>
@@ -12626,7 +12629,7 @@
         <v>228</v>
       </c>
       <c r="E351" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F351" t="s">
         <v>64</v>
@@ -12638,15 +12641,15 @@
         <v>74021</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352" s="3" t="s">
-        <v>364</v>
+        <v>233</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>361</v>
+        <v>408</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>7</v>
@@ -12655,10 +12658,10 @@
         <v>228</v>
       </c>
       <c r="E352" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F352" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G352" t="s">
         <v>14</v>
@@ -12667,15 +12670,15 @@
         <v>74021</v>
       </c>
       <c r="I352" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>7</v>
@@ -12684,7 +12687,7 @@
         <v>228</v>
       </c>
       <c r="E353" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F353" t="s">
         <v>10</v>
@@ -12696,25 +12699,25 @@
         <v>74021</v>
       </c>
       <c r="I353" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A354" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D354" t="s">
+        <v>228</v>
+      </c>
+      <c r="E354" t="s">
         <v>407</v>
       </c>
-      <c r="B354" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D354" t="s">
-        <v>228</v>
-      </c>
-      <c r="E354" t="s">
-        <v>406</v>
-      </c>
       <c r="F354" t="s">
         <v>10</v>
       </c>
@@ -12725,15 +12728,15 @@
         <v>74021</v>
       </c>
       <c r="I354" s="1" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>7</v>
@@ -12742,7 +12745,7 @@
         <v>228</v>
       </c>
       <c r="E355" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F355" t="s">
         <v>10</v>
@@ -12754,15 +12757,15 @@
         <v>74021</v>
       </c>
       <c r="I355" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A356" s="3" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>164</v>
+        <v>411</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>7</v>
@@ -12771,7 +12774,7 @@
         <v>228</v>
       </c>
       <c r="E356" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F356" t="s">
         <v>10</v>
@@ -12783,15 +12786,15 @@
         <v>74021</v>
       </c>
       <c r="I356" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A357" s="3" t="s">
-        <v>177</v>
+        <v>412</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>7</v>
@@ -12800,7 +12803,7 @@
         <v>228</v>
       </c>
       <c r="E357" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F357" t="s">
         <v>10</v>
@@ -12812,15 +12815,15 @@
         <v>74021</v>
       </c>
       <c r="I357" s="1" t="s">
-        <v>345</v>
+        <v>72</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A358" s="3" t="s">
-        <v>400</v>
+        <v>177</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>342</v>
+        <v>107</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>7</v>
@@ -12829,10 +12832,10 @@
         <v>228</v>
       </c>
       <c r="E358" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F358" t="s">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="G358" t="s">
         <v>14</v>
@@ -12841,27 +12844,27 @@
         <v>74021</v>
       </c>
       <c r="I358" s="1" t="s">
-        <v>72</v>
+        <v>345</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A359" s="3" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="B359" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D359" t="s">
+        <v>228</v>
+      </c>
+      <c r="E359" t="s">
         <v>413</v>
       </c>
-      <c r="C359" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D359" t="s">
-        <v>228</v>
-      </c>
-      <c r="E359" t="s">
-        <v>411</v>
-      </c>
       <c r="F359" t="s">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="G359" t="s">
         <v>14</v>
@@ -12870,16 +12873,16 @@
         <v>74021</v>
       </c>
       <c r="I359" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A360" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B360" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B360" s="3" t="s">
-        <v>367</v>
-      </c>
       <c r="C360" s="1" t="s">
         <v>7</v>
       </c>
@@ -12887,10 +12890,10 @@
         <v>228</v>
       </c>
       <c r="E360" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F360" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G360" t="s">
         <v>14</v>
@@ -12904,10 +12907,10 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A361" s="3" t="s">
-        <v>244</v>
+        <v>415</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>200</v>
+        <v>367</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>7</v>
@@ -12916,7 +12919,7 @@
         <v>228</v>
       </c>
       <c r="E361" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F361" t="s">
         <v>10</v>
@@ -12928,85 +12931,85 @@
         <v>74021</v>
       </c>
       <c r="I361" s="1" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A362" s="3" t="s">
-        <v>110</v>
+        <v>244</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>391</v>
+        <v>200</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D362" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E362" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F362" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G362" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H362">
         <v>74021</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>345</v>
+        <v>72</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A363" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D363" t="s">
+        <v>14</v>
+      </c>
+      <c r="E363" t="s">
         <v>416</v>
       </c>
-      <c r="B363" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C363" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D363" t="s">
-        <v>228</v>
-      </c>
-      <c r="E363" t="s">
-        <v>418</v>
-      </c>
       <c r="F363" t="s">
-        <v>209</v>
+        <v>94</v>
       </c>
       <c r="G363" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H363">
         <v>74021</v>
       </c>
       <c r="I363" s="1" t="s">
-        <v>72</v>
+        <v>345</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A364" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D364" t="s">
+        <v>228</v>
+      </c>
+      <c r="E364" t="s">
         <v>419</v>
       </c>
-      <c r="B364" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="C364" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D364" t="s">
-        <v>228</v>
-      </c>
-      <c r="E364" t="s">
-        <v>418</v>
-      </c>
       <c r="F364" t="s">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="G364" t="s">
         <v>14</v>
@@ -13015,15 +13018,15 @@
         <v>74021</v>
       </c>
       <c r="I364" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>304</v>
+        <v>414</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>7</v>
@@ -13032,7 +13035,7 @@
         <v>228</v>
       </c>
       <c r="E365" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F365" t="s">
         <v>64</v>
@@ -13044,27 +13047,27 @@
         <v>74021</v>
       </c>
       <c r="I365" s="1" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A366" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D366" t="s">
+        <v>228</v>
+      </c>
+      <c r="E366" t="s">
         <v>419</v>
       </c>
-      <c r="B366" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C366" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D366" t="s">
-        <v>228</v>
-      </c>
-      <c r="E366" t="s">
-        <v>418</v>
-      </c>
       <c r="F366" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G366" t="s">
         <v>14</v>
@@ -13073,16 +13076,16 @@
         <v>74021</v>
       </c>
       <c r="I366" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A367" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B367" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="B367" s="3" t="s">
-        <v>331</v>
-      </c>
       <c r="C367" s="1" t="s">
         <v>7</v>
       </c>
@@ -13090,7 +13093,7 @@
         <v>228</v>
       </c>
       <c r="E367" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F367" t="s">
         <v>10</v>
@@ -13102,15 +13105,15 @@
         <v>74021</v>
       </c>
       <c r="I367" s="1" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A368" s="3" t="s">
-        <v>246</v>
+        <v>422</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>422</v>
+        <v>331</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>7</v>
@@ -13119,7 +13122,7 @@
         <v>228</v>
       </c>
       <c r="E368" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F368" t="s">
         <v>10</v>
@@ -13131,15 +13134,15 @@
         <v>74021</v>
       </c>
       <c r="I368" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A369" s="3" t="s">
-        <v>400</v>
+        <v>246</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>7</v>
@@ -13148,7 +13151,7 @@
         <v>228</v>
       </c>
       <c r="E369" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F369" t="s">
         <v>10</v>
@@ -13160,15 +13163,15 @@
         <v>74021</v>
       </c>
       <c r="I369" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A370" s="3" t="s">
-        <v>423</v>
+        <v>400</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>424</v>
+        <v>342</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>7</v>
@@ -13177,10 +13180,10 @@
         <v>228</v>
       </c>
       <c r="E370" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="F370" t="s">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="G370" t="s">
         <v>14</v>
@@ -13194,10 +13197,10 @@
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A371" s="3" t="s">
-        <v>324</v>
+        <v>424</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>7</v>
@@ -13206,10 +13209,10 @@
         <v>228</v>
       </c>
       <c r="E371" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F371" t="s">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="G371" t="s">
         <v>14</v>
@@ -13218,24 +13221,24 @@
         <v>74021</v>
       </c>
       <c r="I371" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A372" s="3" t="s">
-        <v>421</v>
+        <v>324</v>
       </c>
       <c r="B372" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D372" t="s">
+        <v>228</v>
+      </c>
+      <c r="E372" t="s">
         <v>426</v>
-      </c>
-      <c r="C372" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D372" t="s">
-        <v>228</v>
-      </c>
-      <c r="E372" t="s">
-        <v>425</v>
       </c>
       <c r="F372" t="s">
         <v>64</v>
@@ -13247,16 +13250,16 @@
         <v>74021</v>
       </c>
       <c r="I372" s="1" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A373" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B373" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B373" s="3" t="s">
-        <v>367</v>
-      </c>
       <c r="C373" s="1" t="s">
         <v>7</v>
       </c>
@@ -13264,10 +13267,10 @@
         <v>228</v>
       </c>
       <c r="E373" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F373" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G373" t="s">
         <v>14</v>
@@ -13276,15 +13279,15 @@
         <v>74021</v>
       </c>
       <c r="I373" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A374" s="3" t="s">
-        <v>244</v>
+        <v>428</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>7</v>
@@ -13293,7 +13296,7 @@
         <v>228</v>
       </c>
       <c r="E374" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F374" t="s">
         <v>10</v>
@@ -13305,44 +13308,44 @@
         <v>74021</v>
       </c>
       <c r="I374" s="1" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A375" s="3" t="s">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>171</v>
+        <v>351</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D375" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E375" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F375" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G375" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H375">
         <v>74021</v>
       </c>
       <c r="I375" s="1" t="s">
-        <v>250</v>
+        <v>72</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A376" s="3" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>7</v>
@@ -13351,7 +13354,7 @@
         <v>14</v>
       </c>
       <c r="E376" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F376" t="s">
         <v>94</v>
@@ -13363,56 +13366,56 @@
         <v>74021</v>
       </c>
       <c r="I376" s="1" t="s">
-        <v>345</v>
+        <v>250</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A377" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D377" t="s">
+        <v>14</v>
+      </c>
+      <c r="E377" t="s">
         <v>429</v>
       </c>
-      <c r="B377" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="C377" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D377" t="s">
-        <v>228</v>
-      </c>
-      <c r="E377" t="s">
-        <v>430</v>
-      </c>
       <c r="F377" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G377" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H377">
         <v>74021</v>
       </c>
       <c r="I377" s="1" t="s">
-        <v>72</v>
+        <v>345</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A378" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D378" t="s">
+        <v>228</v>
+      </c>
+      <c r="E378" t="s">
         <v>431</v>
       </c>
-      <c r="B378" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D378" t="s">
-        <v>228</v>
-      </c>
-      <c r="E378" t="s">
-        <v>430</v>
-      </c>
       <c r="F378" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G378" t="s">
         <v>14</v>
@@ -13421,15 +13424,15 @@
         <v>74021</v>
       </c>
       <c r="I378" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A379" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>426</v>
+        <v>367</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>7</v>
@@ -13438,7 +13441,7 @@
         <v>228</v>
       </c>
       <c r="E379" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F379" t="s">
         <v>10</v>
@@ -13450,73 +13453,73 @@
         <v>74021</v>
       </c>
       <c r="I379" s="1" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A380" s="3" t="s">
-        <v>148</v>
+        <v>430</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>143</v>
+        <v>427</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D380" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E380" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F380" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G380" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H380">
         <v>74021</v>
       </c>
       <c r="I380" s="1" t="s">
-        <v>345</v>
+        <v>72</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A381" s="3" t="s">
-        <v>419</v>
+        <v>147</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>367</v>
+        <v>142</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D381" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E381" t="s">
         <v>433</v>
       </c>
       <c r="F381" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G381" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H381">
         <v>74021</v>
       </c>
       <c r="I381" s="1" t="s">
-        <v>95</v>
+        <v>345</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A382" s="3" t="s">
-        <v>244</v>
+        <v>420</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>426</v>
+        <v>367</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>7</v>
@@ -13525,7 +13528,7 @@
         <v>228</v>
       </c>
       <c r="E382" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F382" t="s">
         <v>10</v>
@@ -13537,44 +13540,44 @@
         <v>74021</v>
       </c>
       <c r="I382" s="1" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A383" s="3" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="B383" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D383" t="s">
+        <v>228</v>
+      </c>
+      <c r="E383" t="s">
         <v>434</v>
       </c>
-      <c r="C383" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D383" t="s">
-        <v>14</v>
-      </c>
-      <c r="E383" t="s">
-        <v>435</v>
-      </c>
       <c r="F383" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G383" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H383">
         <v>74021</v>
       </c>
       <c r="I383" s="1" t="s">
-        <v>250</v>
+        <v>72</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A384" s="3" t="s">
-        <v>110</v>
+        <v>206</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>186</v>
+        <v>435</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>7</v>
@@ -13583,7 +13586,7 @@
         <v>14</v>
       </c>
       <c r="E384" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F384" t="s">
         <v>94</v>
@@ -13595,15 +13598,15 @@
         <v>74021</v>
       </c>
       <c r="I384" s="1" t="s">
-        <v>345</v>
+        <v>250</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
-        <v>251</v>
+        <v>106</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>301</v>
+        <v>186</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>7</v>
@@ -13612,7 +13615,7 @@
         <v>14</v>
       </c>
       <c r="E385" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F385" t="s">
         <v>94</v>
@@ -13624,54 +13627,54 @@
         <v>74021</v>
       </c>
       <c r="I385" s="1" t="s">
-        <v>176</v>
+        <v>345</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A386" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D386" t="s">
+        <v>14</v>
+      </c>
+      <c r="E386" t="s">
         <v>436</v>
       </c>
-      <c r="B386" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C386" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D386" t="s">
-        <v>228</v>
-      </c>
-      <c r="E386" t="s">
-        <v>438</v>
-      </c>
       <c r="F386" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G386" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H386">
         <v>74021</v>
       </c>
       <c r="I386" s="1" t="s">
-        <v>95</v>
+        <v>176</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A387" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B387" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D387" t="s">
+        <v>228</v>
+      </c>
+      <c r="E387" t="s">
         <v>439</v>
       </c>
-      <c r="B387" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C387" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D387" t="s">
-        <v>228</v>
-      </c>
-      <c r="E387" t="s">
-        <v>438</v>
-      </c>
       <c r="F387" t="s">
         <v>10</v>
       </c>
@@ -13682,15 +13685,15 @@
         <v>74021</v>
       </c>
       <c r="I387" s="1" t="s">
-        <v>345</v>
+        <v>95</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A388" s="3" t="s">
-        <v>350</v>
+        <v>440</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>367</v>
+        <v>441</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>7</v>
@@ -13699,7 +13702,7 @@
         <v>228</v>
       </c>
       <c r="E388" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F388" t="s">
         <v>10</v>
@@ -13711,25 +13714,25 @@
         <v>74021</v>
       </c>
       <c r="I388" s="1" t="s">
-        <v>95</v>
+        <v>345</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A389" s="3" t="s">
-        <v>148</v>
+        <v>350</v>
       </c>
       <c r="B389" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D389" t="s">
+        <v>228</v>
+      </c>
+      <c r="E389" t="s">
         <v>442</v>
       </c>
-      <c r="C389" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D389" t="s">
-        <v>228</v>
-      </c>
-      <c r="E389" t="s">
-        <v>441</v>
-      </c>
       <c r="F389" t="s">
         <v>10</v>
       </c>
@@ -13740,30 +13743,30 @@
         <v>74021</v>
       </c>
       <c r="I389" s="1" t="s">
-        <v>345</v>
+        <v>95</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A390" s="3" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>107</v>
+        <v>443</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D390" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E390" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F390" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G390" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H390">
         <v>74021</v>
@@ -13774,25 +13777,25 @@
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A391" s="3" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D391" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E391" t="s">
         <v>444</v>
       </c>
       <c r="F391" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G391" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H391">
         <v>74021</v>
@@ -13803,25 +13806,25 @@
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A392" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D392" t="s">
+        <v>228</v>
+      </c>
+      <c r="E392" t="s">
         <v>445</v>
       </c>
-      <c r="B392" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C392" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D392" t="s">
-        <v>14</v>
-      </c>
-      <c r="E392" t="s">
-        <v>446</v>
-      </c>
       <c r="F392" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G392" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H392">
         <v>74021</v>
@@ -13832,31 +13835,31 @@
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A393" s="3" t="s">
-        <v>394</v>
+        <v>446</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>367</v>
+        <v>258</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D393" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E393" t="s">
         <v>447</v>
       </c>
       <c r="F393" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G393" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H393">
         <v>74021</v>
       </c>
       <c r="I393" s="1" t="s">
-        <v>95</v>
+        <v>345</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.35">
@@ -13873,10 +13876,10 @@
         <v>228</v>
       </c>
       <c r="E394" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F394" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G394" t="s">
         <v>14</v>
@@ -13890,68 +13893,68 @@
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A395" s="3" t="s">
-        <v>98</v>
+        <v>394</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>161</v>
+        <v>367</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D395" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E395" t="s">
         <v>448</v>
       </c>
       <c r="F395" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G395" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H395">
         <v>74021</v>
       </c>
       <c r="I395" s="1" t="s">
-        <v>345</v>
+        <v>95</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A396" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D396" t="s">
+        <v>14</v>
+      </c>
+      <c r="E396" t="s">
         <v>449</v>
       </c>
-      <c r="B396" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C396" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D396" t="s">
-        <v>228</v>
-      </c>
-      <c r="E396" t="s">
-        <v>450</v>
-      </c>
       <c r="F396" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G396" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H396">
         <v>74021</v>
       </c>
       <c r="I396" s="1" t="s">
-        <v>95</v>
+        <v>345</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A397" s="3" t="s">
-        <v>118</v>
+        <v>450</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>149</v>
+        <v>367</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>7</v>
@@ -13960,7 +13963,7 @@
         <v>228</v>
       </c>
       <c r="E397" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F397" t="s">
         <v>10</v>
@@ -13972,44 +13975,44 @@
         <v>74021</v>
       </c>
       <c r="I397" s="1" t="s">
-        <v>345</v>
+        <v>95</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A398" s="3" t="s">
-        <v>181</v>
+        <v>117</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>334</v>
+        <v>148</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D398" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E398" t="s">
         <v>451</v>
       </c>
       <c r="F398" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G398" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H398">
         <v>74021</v>
       </c>
       <c r="I398" s="1" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A399" s="3" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>111</v>
+        <v>334</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>7</v>
@@ -14018,7 +14021,7 @@
         <v>14</v>
       </c>
       <c r="E399" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F399" t="s">
         <v>94</v>
@@ -14030,30 +14033,30 @@
         <v>74021</v>
       </c>
       <c r="I399" s="1" t="s">
-        <v>345</v>
+        <v>250</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A400" s="3" t="s">
-        <v>257</v>
+        <v>144</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>249</v>
+        <v>110</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D400" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E400" t="s">
         <v>452</v>
       </c>
       <c r="F400" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G400" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H400">
         <v>74021</v>
@@ -14064,39 +14067,39 @@
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A401" s="3" t="s">
-        <v>131</v>
+        <v>257</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D401" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E401" t="s">
         <v>453</v>
       </c>
       <c r="F401" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G401" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H401">
         <v>74021</v>
       </c>
       <c r="I401" s="1" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A402" s="3" t="s">
-        <v>281</v>
+        <v>130</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>104</v>
+        <v>217</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>7</v>
@@ -14105,7 +14108,7 @@
         <v>14</v>
       </c>
       <c r="E402" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F402" t="s">
         <v>94</v>
@@ -14117,15 +14120,15 @@
         <v>74021</v>
       </c>
       <c r="I402" s="1" t="s">
-        <v>345</v>
+        <v>250</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A403" s="3" t="s">
-        <v>181</v>
+        <v>281</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>334</v>
+        <v>104</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>7</v>
@@ -14146,24 +14149,24 @@
         <v>74021</v>
       </c>
       <c r="I403" s="1" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A404" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B404" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D404" t="s">
+        <v>14</v>
+      </c>
+      <c r="E404" t="s">
         <v>455</v>
-      </c>
-      <c r="B404" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C404" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D404" t="s">
-        <v>14</v>
-      </c>
-      <c r="E404" t="s">
-        <v>454</v>
       </c>
       <c r="F404" t="s">
         <v>94</v>
@@ -14175,15 +14178,15 @@
         <v>74021</v>
       </c>
       <c r="I404" s="1" t="s">
-        <v>345</v>
+        <v>250</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A405" s="3" t="s">
-        <v>145</v>
+        <v>456</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>456</v>
+        <v>92</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>7</v>
@@ -14192,7 +14195,7 @@
         <v>14</v>
       </c>
       <c r="E405" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F405" t="s">
         <v>94</v>
@@ -14209,77 +14212,77 @@
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A406" s="3" t="s">
-        <v>233</v>
+        <v>144</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>164</v>
+        <v>457</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D406" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E406" t="s">
         <v>458</v>
       </c>
       <c r="F406" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G406" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H406">
         <v>74021</v>
       </c>
       <c r="I406" s="1" t="s">
-        <v>59</v>
+        <v>345</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A407" s="3" t="s">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D407" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E407" t="s">
         <v>459</v>
       </c>
       <c r="F407" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G407" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H407">
         <v>74021</v>
       </c>
       <c r="I407" s="1" t="s">
-        <v>250</v>
+        <v>59</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A408" s="3" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="B408" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D408" t="s">
+        <v>14</v>
+      </c>
+      <c r="E408" t="s">
         <v>460</v>
-      </c>
-      <c r="C408" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D408" t="s">
-        <v>14</v>
-      </c>
-      <c r="E408" t="s">
-        <v>459</v>
       </c>
       <c r="F408" t="s">
         <v>94</v>
@@ -14291,12 +14294,12 @@
         <v>74021</v>
       </c>
       <c r="I408" s="1" t="s">
-        <v>345</v>
+        <v>250</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A409" s="3" t="s">
-        <v>257</v>
+        <v>117</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>461</v>
@@ -14305,16 +14308,16 @@
         <v>7</v>
       </c>
       <c r="D409" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E409" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F409" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G409" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H409">
         <v>74021</v>
@@ -14325,25 +14328,25 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A410" s="3" t="s">
-        <v>109</v>
+        <v>257</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>111</v>
+        <v>462</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D410" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E410" t="s">
         <v>463</v>
       </c>
       <c r="F410" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G410" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H410">
         <v>74021</v>
@@ -14354,49 +14357,49 @@
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A411" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D411" t="s">
+        <v>14</v>
+      </c>
+      <c r="E411" t="s">
         <v>464</v>
       </c>
-      <c r="B411" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C411" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D411" t="s">
-        <v>228</v>
-      </c>
-      <c r="E411" t="s">
-        <v>465</v>
-      </c>
       <c r="F411" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G411" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H411">
         <v>74021</v>
       </c>
       <c r="I411" s="1" t="s">
-        <v>59</v>
+        <v>345</v>
       </c>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A412" s="3" t="s">
-        <v>106</v>
+        <v>465</v>
       </c>
       <c r="B412" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D412" t="s">
+        <v>228</v>
+      </c>
+      <c r="E412" t="s">
         <v>466</v>
       </c>
-      <c r="C412" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D412" t="s">
-        <v>228</v>
-      </c>
-      <c r="E412" t="s">
-        <v>465</v>
-      </c>
       <c r="F412" t="s">
         <v>10</v>
       </c>
@@ -14407,131 +14410,131 @@
         <v>74021</v>
       </c>
       <c r="I412" s="1" t="s">
-        <v>345</v>
+        <v>59</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A413" s="3" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>164</v>
+        <v>467</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D413" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E413" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F413" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G413" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H413">
         <v>74021</v>
       </c>
       <c r="I413" s="1" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A414" s="3" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>264</v>
+        <v>164</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D414" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E414" t="s">
         <v>468</v>
       </c>
       <c r="F414" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G414" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H414">
         <v>74021</v>
       </c>
       <c r="I414" s="1" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A415" s="3" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D415" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E415" t="s">
         <v>469</v>
       </c>
       <c r="F415" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G415" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H415">
         <v>74021</v>
       </c>
       <c r="I415" s="1" t="s">
-        <v>250</v>
+        <v>59</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A416" s="3" t="s">
-        <v>299</v>
+        <v>181</v>
       </c>
       <c r="B416" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D416" t="s">
+        <v>14</v>
+      </c>
+      <c r="E416" t="s">
         <v>470</v>
       </c>
-      <c r="C416" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D416" t="s">
-        <v>228</v>
-      </c>
-      <c r="E416" t="s">
-        <v>471</v>
-      </c>
       <c r="F416" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G416" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H416">
         <v>74021</v>
       </c>
       <c r="I416" s="1" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A417" s="3" t="s">
-        <v>341</v>
+        <v>299</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>422</v>
+        <v>471</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>7</v>
@@ -14540,10 +14543,10 @@
         <v>228</v>
       </c>
       <c r="E417" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F417" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G417" t="s">
         <v>14</v>
@@ -14557,97 +14560,97 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A418" s="3" t="s">
-        <v>181</v>
+        <v>341</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>164</v>
+        <v>423</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D418" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E418" t="s">
         <v>472</v>
       </c>
       <c r="F418" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G418" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H418">
         <v>74021</v>
       </c>
       <c r="I418" s="1" t="s">
-        <v>250</v>
+        <v>59</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A419" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D419" t="s">
+        <v>14</v>
+      </c>
+      <c r="E419" t="s">
         <v>473</v>
       </c>
-      <c r="B419" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C419" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D419" t="s">
-        <v>228</v>
-      </c>
-      <c r="E419" t="s">
-        <v>474</v>
-      </c>
       <c r="F419" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G419" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H419">
         <v>74021</v>
       </c>
       <c r="I419" s="1" t="s">
-        <v>345</v>
+        <v>250</v>
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A420" s="3" t="s">
-        <v>181</v>
+        <v>474</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D420" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E420" t="s">
         <v>475</v>
       </c>
       <c r="F420" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G420" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H420">
         <v>74021</v>
       </c>
       <c r="I420" s="1" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A421" s="3" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>466</v>
+        <v>216</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>7</v>
@@ -14656,7 +14659,7 @@
         <v>14</v>
       </c>
       <c r="E421" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F421" t="s">
         <v>94</v>
@@ -14668,24 +14671,24 @@
         <v>74021</v>
       </c>
       <c r="I421" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A422" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B422" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D422" t="s">
+        <v>14</v>
+      </c>
+      <c r="E422" t="s">
         <v>476</v>
-      </c>
-      <c r="B422" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D422" t="s">
-        <v>14</v>
-      </c>
-      <c r="E422" t="s">
-        <v>475</v>
       </c>
       <c r="F422" t="s">
         <v>94</v>
@@ -14697,15 +14700,15 @@
         <v>74021</v>
       </c>
       <c r="I422" s="1" t="s">
-        <v>345</v>
+        <v>253</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A423" s="3" t="s">
-        <v>226</v>
+        <v>477</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>7</v>
@@ -14714,7 +14717,7 @@
         <v>14</v>
       </c>
       <c r="E423" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F423" t="s">
         <v>94</v>
@@ -14726,131 +14729,131 @@
         <v>74021</v>
       </c>
       <c r="I423" s="1" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A424" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D424" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E424" t="s">
         <v>478</v>
       </c>
       <c r="F424" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G424" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H424">
         <v>74021</v>
       </c>
       <c r="I424" s="1" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D425" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E425" t="s">
         <v>479</v>
       </c>
       <c r="F425" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G425" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H425">
         <v>74021</v>
       </c>
       <c r="I425" s="1" t="s">
-        <v>250</v>
+        <v>59</v>
       </c>
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A426" s="3" t="s">
-        <v>341</v>
+        <v>230</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D426" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E426" t="s">
         <v>480</v>
       </c>
       <c r="F426" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G426" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H426">
         <v>74021</v>
       </c>
       <c r="I426" s="1" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A427" s="3" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D427" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E427" t="s">
         <v>481</v>
       </c>
       <c r="F427" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G427" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H427">
         <v>74021</v>
       </c>
       <c r="I427" s="1" t="s">
-        <v>250</v>
+        <v>59</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A428" s="3" t="s">
-        <v>305</v>
+        <v>130</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>7</v>
@@ -14859,10 +14862,10 @@
         <v>14</v>
       </c>
       <c r="E428" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F428" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G428" t="s">
         <v>11</v>
@@ -14876,10 +14879,10 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A429" s="3" t="s">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>334</v>
+        <v>217</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>7</v>
@@ -14891,7 +14894,7 @@
         <v>482</v>
       </c>
       <c r="F429" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="G429" t="s">
         <v>11</v>
@@ -14908,7 +14911,7 @@
         <v>230</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>210</v>
+        <v>334</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>7</v>
@@ -14917,10 +14920,10 @@
         <v>14</v>
       </c>
       <c r="E430" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F430" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G430" t="s">
         <v>11</v>
@@ -14934,39 +14937,39 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A431" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B431" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C431" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D431" t="s">
+        <v>14</v>
+      </c>
+      <c r="E431" t="s">
         <v>483</v>
       </c>
-      <c r="B431" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="C431" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D431" t="s">
-        <v>228</v>
-      </c>
-      <c r="E431" t="s">
-        <v>485</v>
-      </c>
       <c r="F431" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G431" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H431">
         <v>74021</v>
       </c>
       <c r="I431" s="1" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A432" s="3" t="s">
-        <v>283</v>
+        <v>484</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>331</v>
+        <v>485</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>7</v>
@@ -14975,7 +14978,7 @@
         <v>228</v>
       </c>
       <c r="E432" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F432" t="s">
         <v>10</v>
@@ -14987,25 +14990,25 @@
         <v>74021</v>
       </c>
       <c r="I432" s="1" t="s">
-        <v>176</v>
+        <v>59</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A433" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B433" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C433" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D433" t="s">
+        <v>228</v>
+      </c>
+      <c r="E433" t="s">
         <v>486</v>
       </c>
-      <c r="B433" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C433" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D433" t="s">
-        <v>228</v>
-      </c>
-      <c r="E433" t="s">
-        <v>485</v>
-      </c>
       <c r="F433" t="s">
         <v>10</v>
       </c>
@@ -15016,15 +15019,15 @@
         <v>74021</v>
       </c>
       <c r="I433" s="1" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A434" s="3" t="s">
-        <v>289</v>
+        <v>487</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>487</v>
+        <v>294</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>7</v>
@@ -15033,7 +15036,7 @@
         <v>228</v>
       </c>
       <c r="E434" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F434" t="s">
         <v>10</v>
@@ -15045,15 +15048,15 @@
         <v>74021</v>
       </c>
       <c r="I434" s="1" t="s">
-        <v>176</v>
+        <v>59</v>
       </c>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A435" s="3" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>124</v>
+        <v>488</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>7</v>
@@ -15062,7 +15065,7 @@
         <v>228</v>
       </c>
       <c r="E435" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F435" t="s">
         <v>10</v>
@@ -15074,44 +15077,44 @@
         <v>74021</v>
       </c>
       <c r="I435" s="1" t="s">
-        <v>345</v>
+        <v>176</v>
       </c>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A436" s="3" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>334</v>
+        <v>123</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D436" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E436" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F436" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G436" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H436">
         <v>74021</v>
       </c>
       <c r="I436" s="1" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A437" s="3" t="s">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>207</v>
+        <v>334</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>7</v>
@@ -15120,10 +15123,10 @@
         <v>14</v>
       </c>
       <c r="E437" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F437" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G437" t="s">
         <v>11</v>
@@ -15137,10 +15140,10 @@
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A438" s="3" t="s">
-        <v>226</v>
+        <v>130</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>7</v>
@@ -15152,7 +15155,7 @@
         <v>489</v>
       </c>
       <c r="F438" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="G438" t="s">
         <v>11</v>
@@ -15166,10 +15169,10 @@
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A439" s="3" t="s">
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>7</v>
@@ -15178,10 +15181,10 @@
         <v>14</v>
       </c>
       <c r="E439" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F439" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G439" t="s">
         <v>11</v>
@@ -15195,39 +15198,39 @@
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A440" s="3" t="s">
-        <v>305</v>
+        <v>163</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D440" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E440" t="s">
         <v>490</v>
       </c>
       <c r="F440" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G440" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H440">
         <v>74021</v>
       </c>
       <c r="I440" s="1" t="s">
-        <v>176</v>
+        <v>250</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A441" s="3" t="s">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>487</v>
+        <v>216</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>7</v>
@@ -15253,39 +15256,39 @@
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A442" s="3" t="s">
-        <v>219</v>
+        <v>130</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>196</v>
+        <v>488</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D442" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E442" t="s">
         <v>492</v>
       </c>
       <c r="F442" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G442" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H442">
         <v>74021</v>
       </c>
       <c r="I442" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A443" s="3" t="s">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>7</v>
@@ -15294,7 +15297,7 @@
         <v>14</v>
       </c>
       <c r="E443" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F443" t="s">
         <v>94</v>
@@ -15306,15 +15309,15 @@
         <v>74021</v>
       </c>
       <c r="I443" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A444" s="3" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>7</v>
@@ -15335,15 +15338,15 @@
         <v>74021</v>
       </c>
       <c r="I444" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A445" s="3" t="s">
-        <v>305</v>
+        <v>181</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>334</v>
+        <v>207</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>7</v>
@@ -15364,102 +15367,102 @@
         <v>74021</v>
       </c>
       <c r="I445" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A446" s="3" t="s">
-        <v>233</v>
+        <v>305</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>405</v>
+        <v>334</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D446" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E446" t="s">
         <v>495</v>
       </c>
       <c r="F446" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G446" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H446">
         <v>74021</v>
       </c>
       <c r="I446" s="1" t="s">
-        <v>176</v>
+        <v>250</v>
       </c>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A447" s="3" t="s">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>196</v>
+        <v>408</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D447" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E447" t="s">
         <v>496</v>
       </c>
       <c r="F447" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G447" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H447">
         <v>74021</v>
       </c>
       <c r="I447" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A448" s="3" t="s">
-        <v>483</v>
+        <v>181</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>344</v>
+        <v>196</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D448" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E448" t="s">
         <v>497</v>
       </c>
       <c r="F448" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G448" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H448">
         <v>74021</v>
       </c>
       <c r="I448" s="1" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A449" s="3" t="s">
-        <v>233</v>
+        <v>484</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>7</v>
@@ -15485,242 +15488,242 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A450" s="3" t="s">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>334</v>
+        <v>196</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D450" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E450" t="s">
         <v>499</v>
       </c>
       <c r="F450" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G450" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H450">
         <v>74021</v>
       </c>
       <c r="I450" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A451" s="3" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>294</v>
+        <v>334</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D451" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E451" t="s">
         <v>500</v>
       </c>
       <c r="F451" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G451" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H451">
         <v>74021</v>
       </c>
       <c r="I451" s="1" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A452" s="3" t="s">
-        <v>131</v>
+        <v>242</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D452" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E452" t="s">
         <v>501</v>
       </c>
       <c r="F452" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="G452" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H452">
         <v>74021</v>
       </c>
       <c r="I452" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A453" s="3" t="s">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D453" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E453" t="s">
         <v>502</v>
       </c>
       <c r="F453" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G453" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H453">
         <v>74021</v>
       </c>
       <c r="I453" s="1" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A454" s="3" t="s">
-        <v>131</v>
+        <v>233</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D454" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E454" t="s">
         <v>503</v>
       </c>
       <c r="F454" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G454" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H454">
         <v>74021</v>
       </c>
       <c r="I454" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A455" s="3" t="s">
-        <v>299</v>
+        <v>130</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D455" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="E455" t="s">
         <v>504</v>
       </c>
       <c r="F455" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G455" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H455">
         <v>74021</v>
       </c>
       <c r="I455" s="1" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A456" s="3" t="s">
-        <v>131</v>
+        <v>299</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D456" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E456" t="s">
         <v>505</v>
       </c>
       <c r="F456" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G456" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H456">
         <v>74021</v>
       </c>
       <c r="I456" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A457" s="3" t="s">
-        <v>246</v>
+        <v>130</v>
       </c>
       <c r="B457" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C457" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D457" t="s">
+        <v>14</v>
+      </c>
+      <c r="E457" t="s">
         <v>506</v>
       </c>
-      <c r="C457" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D457" t="s">
-        <v>228</v>
-      </c>
-      <c r="E457" t="s">
-        <v>507</v>
-      </c>
       <c r="F457" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G457" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H457">
         <v>74021</v>
       </c>
       <c r="I457" s="1" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A458" s="3" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>149</v>
+        <v>507</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>7</v>
@@ -15732,7 +15735,7 @@
         <v>508</v>
       </c>
       <c r="F458" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G458" t="s">
         <v>14</v>
@@ -15746,31 +15749,31 @@
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A459" s="3" t="s">
-        <v>181</v>
+        <v>267</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D459" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E459" t="s">
         <v>509</v>
       </c>
       <c r="F459" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G459" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H459">
         <v>74021</v>
       </c>
       <c r="I459" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.35">
@@ -15807,7 +15810,7 @@
         <v>181</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>7</v>
@@ -15816,10 +15819,10 @@
         <v>14</v>
       </c>
       <c r="E461" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F461" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G461" t="s">
         <v>11</v>
@@ -15848,7 +15851,7 @@
         <v>511</v>
       </c>
       <c r="F462" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="G462" t="s">
         <v>11</v>
@@ -15865,7 +15868,7 @@
         <v>181</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>7</v>
@@ -15894,7 +15897,7 @@
         <v>181</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>7</v>
@@ -15952,7 +15955,7 @@
         <v>181</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>7</v>
@@ -15961,10 +15964,10 @@
         <v>14</v>
       </c>
       <c r="E466" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F466" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G466" t="s">
         <v>11</v>
@@ -15978,22 +15981,22 @@
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A467" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B467" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C467" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D467" t="s">
+        <v>14</v>
+      </c>
+      <c r="E467" t="s">
         <v>515</v>
       </c>
-      <c r="B467" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="C467" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D467" t="s">
-        <v>517</v>
-      </c>
-      <c r="E467" t="s">
-        <v>518</v>
-      </c>
       <c r="F467" t="s">
-        <v>519</v>
+        <v>64</v>
       </c>
       <c r="G467" t="s">
         <v>11</v>
@@ -16002,27 +16005,27 @@
         <v>74021</v>
       </c>
       <c r="I467" s="1" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A468" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B468" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C468" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D468" t="s">
+        <v>518</v>
+      </c>
+      <c r="E468" t="s">
+        <v>519</v>
+      </c>
+      <c r="F468" t="s">
         <v>520</v>
-      </c>
-      <c r="B468" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="C468" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D468" t="s">
-        <v>517</v>
-      </c>
-      <c r="E468" t="s">
-        <v>522</v>
-      </c>
-      <c r="F468" t="s">
-        <v>519</v>
       </c>
       <c r="G468" t="s">
         <v>11</v>
@@ -16036,22 +16039,22 @@
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A469" s="3" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B469" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C469" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D469" t="s">
+        <v>518</v>
+      </c>
+      <c r="E469" t="s">
         <v>523</v>
       </c>
-      <c r="C469" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D469" t="s">
-        <v>517</v>
-      </c>
-      <c r="E469" t="s">
-        <v>524</v>
-      </c>
       <c r="F469" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="G469" t="s">
         <v>11</v>
@@ -16065,22 +16068,22 @@
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A470" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B470" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D470" t="s">
+        <v>518</v>
+      </c>
+      <c r="E470" t="s">
+        <v>525</v>
+      </c>
+      <c r="F470" t="s">
         <v>526</v>
-      </c>
-      <c r="B470" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C470" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D470" t="s">
-        <v>14</v>
-      </c>
-      <c r="E470" t="s">
-        <v>528</v>
-      </c>
-      <c r="F470" t="s">
-        <v>519</v>
       </c>
       <c r="G470" t="s">
         <v>11</v>
@@ -16094,22 +16097,22 @@
     </row>
     <row r="471" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A471" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B471" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D471" t="s">
+        <v>14</v>
+      </c>
+      <c r="E471" t="s">
         <v>529</v>
       </c>
-      <c r="B471" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="C471" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D471" t="s">
-        <v>517</v>
-      </c>
-      <c r="E471" t="s">
-        <v>531</v>
-      </c>
       <c r="F471" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G471" t="s">
         <v>11</v>
@@ -16123,22 +16126,22 @@
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A472" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B472" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C472" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D472" t="s">
+        <v>518</v>
+      </c>
+      <c r="E472" t="s">
         <v>532</v>
       </c>
-      <c r="B472" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C472" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D472" t="s">
-        <v>14</v>
-      </c>
-      <c r="E472" t="s">
-        <v>533</v>
-      </c>
       <c r="F472" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G472" t="s">
         <v>11</v>
@@ -16152,10 +16155,10 @@
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A473" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>7</v>
@@ -16167,7 +16170,7 @@
         <v>534</v>
       </c>
       <c r="F473" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G473" t="s">
         <v>11</v>
@@ -16181,22 +16184,22 @@
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A474" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B474" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C474" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D474" t="s">
+        <v>14</v>
+      </c>
+      <c r="E474" t="s">
         <v>535</v>
       </c>
-      <c r="B474" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C474" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D474" t="s">
-        <v>14</v>
-      </c>
-      <c r="E474" t="s">
-        <v>536</v>
-      </c>
       <c r="F474" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="G474" t="s">
         <v>11</v>
@@ -16210,22 +16213,22 @@
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A475" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="B475" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D475" t="s">
+        <v>14</v>
+      </c>
+      <c r="E475" t="s">
+        <v>537</v>
+      </c>
+      <c r="F475" t="s">
         <v>538</v>
-      </c>
-      <c r="B475" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="C475" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D475" t="s">
-        <v>14</v>
-      </c>
-      <c r="E475" t="s">
-        <v>540</v>
-      </c>
-      <c r="F475" t="s">
-        <v>519</v>
       </c>
       <c r="G475" t="s">
         <v>11</v>
@@ -16239,22 +16242,22 @@
     </row>
     <row r="476" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A476" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B476" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D476" t="s">
+        <v>14</v>
+      </c>
+      <c r="E476" t="s">
         <v>541</v>
       </c>
-      <c r="B476" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="C476" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D476" t="s">
-        <v>517</v>
-      </c>
-      <c r="E476" t="s">
-        <v>540</v>
-      </c>
       <c r="F476" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G476" t="s">
         <v>11</v>
@@ -16268,22 +16271,22 @@
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A477" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B477" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="B477" s="3" t="s">
-        <v>544</v>
-      </c>
       <c r="C477" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D477" t="s">
-        <v>14</v>
+        <v>518</v>
       </c>
       <c r="E477" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F477" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G477" t="s">
         <v>11</v>
@@ -16297,22 +16300,22 @@
     </row>
     <row r="478" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A478" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B478" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C478" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D478" t="s">
+        <v>14</v>
+      </c>
+      <c r="E478" t="s">
         <v>546</v>
       </c>
-      <c r="B478" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="C478" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D478" t="s">
-        <v>14</v>
-      </c>
-      <c r="E478" t="s">
-        <v>548</v>
-      </c>
       <c r="F478" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G478" t="s">
         <v>11</v>
@@ -16326,22 +16329,22 @@
     </row>
     <row r="479" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A479" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B479" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D479" t="s">
+        <v>14</v>
+      </c>
+      <c r="E479" t="s">
         <v>549</v>
       </c>
-      <c r="B479" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C479" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D479" t="s">
-        <v>14</v>
-      </c>
-      <c r="E479" t="s">
-        <v>550</v>
-      </c>
       <c r="F479" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="G479" t="s">
         <v>11</v>
@@ -16355,22 +16358,22 @@
     </row>
     <row r="480" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A480" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B480" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D480" t="s">
+        <v>14</v>
+      </c>
+      <c r="E480" t="s">
         <v>551</v>
       </c>
-      <c r="B480" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C480" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D480" t="s">
-        <v>14</v>
-      </c>
-      <c r="E480" t="s">
-        <v>552</v>
-      </c>
       <c r="F480" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="G480" t="s">
         <v>11</v>
@@ -16384,10 +16387,10 @@
     </row>
     <row r="481" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A481" s="3" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>7</v>
@@ -16399,7 +16402,7 @@
         <v>553</v>
       </c>
       <c r="F481" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G481" t="s">
         <v>11</v>
@@ -16413,22 +16416,22 @@
     </row>
     <row r="482" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A482" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B482" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D482" t="s">
+        <v>14</v>
+      </c>
+      <c r="E482" t="s">
         <v>554</v>
       </c>
-      <c r="B482" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="C482" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D482" t="s">
-        <v>14</v>
-      </c>
-      <c r="E482" t="s">
-        <v>556</v>
-      </c>
       <c r="F482" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G482" t="s">
         <v>11</v>
@@ -16442,22 +16445,22 @@
     </row>
     <row r="483" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A483" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B483" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D483" t="s">
+        <v>14</v>
+      </c>
+      <c r="E483" t="s">
         <v>557</v>
       </c>
-      <c r="B483" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="C483" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D483" t="s">
-        <v>517</v>
-      </c>
-      <c r="E483" t="s">
-        <v>559</v>
-      </c>
       <c r="F483" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G483" t="s">
         <v>11</v>
@@ -16471,22 +16474,22 @@
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A484" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B484" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D484" t="s">
+        <v>518</v>
+      </c>
+      <c r="E484" t="s">
         <v>560</v>
       </c>
-      <c r="B484" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="C484" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D484" t="s">
-        <v>517</v>
-      </c>
-      <c r="E484" t="s">
-        <v>562</v>
-      </c>
       <c r="F484" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="G484" t="s">
         <v>11</v>
@@ -16500,22 +16503,22 @@
     </row>
     <row r="485" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A485" s="3" t="s">
-        <v>515</v>
+        <v>561</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D485" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E485" t="s">
         <v>563</v>
       </c>
       <c r="F485" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G485" t="s">
         <v>11</v>
@@ -16529,22 +16532,22 @@
     </row>
     <row r="486" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A486" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B486" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C486" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D486" t="s">
+        <v>518</v>
+      </c>
+      <c r="E486" t="s">
         <v>564</v>
       </c>
-      <c r="B486" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="C486" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D486" t="s">
-        <v>517</v>
-      </c>
-      <c r="E486" t="s">
-        <v>566</v>
-      </c>
       <c r="F486" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="G486" t="s">
         <v>11</v>
@@ -16558,22 +16561,22 @@
     </row>
     <row r="487" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A487" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B487" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C487" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D487" t="s">
+        <v>518</v>
+      </c>
+      <c r="E487" t="s">
         <v>567</v>
       </c>
-      <c r="B487" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C487" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D487" t="s">
-        <v>11</v>
-      </c>
-      <c r="E487" t="s">
-        <v>568</v>
-      </c>
       <c r="F487" t="s">
-        <v>569</v>
+        <v>520</v>
       </c>
       <c r="G487" t="s">
         <v>11</v>
@@ -16582,41 +16585,41 @@
         <v>74021</v>
       </c>
       <c r="I487" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="488" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A488" s="3" t="s">
-        <v>17</v>
+        <v>568</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>25</v>
+        <v>301</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D488" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E488" t="s">
+        <v>569</v>
+      </c>
+      <c r="F488" t="s">
         <v>570</v>
       </c>
-      <c r="F488" t="s">
-        <v>11</v>
-      </c>
       <c r="G488" t="s">
-        <v>228</v>
+        <v>11</v>
       </c>
       <c r="H488">
         <v>74021</v>
       </c>
       <c r="I488" s="1" t="s">
-        <v>345</v>
+        <v>253</v>
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A489" s="3" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B489" s="3" t="s">
         <v>25</v>
@@ -16634,7 +16637,7 @@
         <v>11</v>
       </c>
       <c r="G489" t="s">
-        <v>11</v>
+        <v>228</v>
       </c>
       <c r="H489">
         <v>74021</v>
@@ -16674,16 +16677,16 @@
     </row>
     <row r="491" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A491" s="3" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D491" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E491" t="s">
         <v>573</v>
@@ -16706,16 +16709,16 @@
         <v>17</v>
       </c>
       <c r="B492" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D492" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E492" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F492" t="s">
         <v>11</v>
@@ -16732,22 +16735,22 @@
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A493" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B493" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C493" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D493" t="s">
+        <v>8</v>
+      </c>
+      <c r="E493" t="s">
         <v>574</v>
       </c>
-      <c r="B493" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="C493" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D493" t="s">
-        <v>11</v>
-      </c>
-      <c r="E493" t="s">
-        <v>576</v>
-      </c>
       <c r="F493" t="s">
-        <v>209</v>
+        <v>11</v>
       </c>
       <c r="G493" t="s">
         <v>11</v>
@@ -16756,15 +16759,15 @@
         <v>74021</v>
       </c>
       <c r="I493" s="1" t="s">
-        <v>59</v>
+        <v>345</v>
       </c>
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A494" s="3" t="s">
-        <v>66</v>
+        <v>575</v>
       </c>
       <c r="B494" s="3" t="s">
-        <v>47</v>
+        <v>576</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>7</v>
@@ -16773,10 +16776,10 @@
         <v>11</v>
       </c>
       <c r="E494" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F494" t="s">
-        <v>577</v>
+        <v>209</v>
       </c>
       <c r="G494" t="s">
         <v>11</v>
@@ -16790,23 +16793,23 @@
     </row>
     <row r="495" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A495" s="3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B495" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C495" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D495" t="s">
+        <v>11</v>
+      </c>
+      <c r="E495" t="s">
+        <v>577</v>
+      </c>
+      <c r="F495" t="s">
         <v>578</v>
       </c>
-      <c r="C495" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D495" t="s">
-        <v>517</v>
-      </c>
-      <c r="E495" t="s">
-        <v>579</v>
-      </c>
-      <c r="F495" t="s">
-        <v>10</v>
-      </c>
       <c r="G495" t="s">
         <v>11</v>
       </c>
@@ -16814,25 +16817,25 @@
         <v>74021</v>
       </c>
       <c r="I495" s="1" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A496" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C496" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D496" t="s">
+        <v>518</v>
+      </c>
+      <c r="E496" t="s">
         <v>580</v>
       </c>
-      <c r="B496" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D496" t="s">
-        <v>517</v>
-      </c>
-      <c r="E496" t="s">
-        <v>579</v>
-      </c>
       <c r="F496" t="s">
         <v>10</v>
       </c>
@@ -16843,24 +16846,24 @@
         <v>74021</v>
       </c>
       <c r="I496" s="1" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A497" s="3" t="s">
-        <v>77</v>
+        <v>581</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>34</v>
+        <v>582</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D497" t="s">
-        <v>228</v>
+        <v>518</v>
       </c>
       <c r="E497" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F497" t="s">
         <v>10</v>
@@ -16872,25 +16875,25 @@
         <v>74021</v>
       </c>
       <c r="I497" s="1" t="s">
-        <v>345</v>
+        <v>95</v>
       </c>
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A498" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B498" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C498" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D498" t="s">
+        <v>228</v>
+      </c>
+      <c r="E498" t="s">
         <v>583</v>
       </c>
-      <c r="B498" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="C498" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D498" t="s">
-        <v>517</v>
-      </c>
-      <c r="E498" t="s">
-        <v>582</v>
-      </c>
       <c r="F498" t="s">
         <v>10</v>
       </c>
@@ -16901,24 +16904,24 @@
         <v>74021</v>
       </c>
       <c r="I498" s="1" t="s">
-        <v>16</v>
+        <v>345</v>
       </c>
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A499" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B499" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B499" s="3" t="s">
-        <v>586</v>
-      </c>
       <c r="C499" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D499" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E499" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F499" t="s">
         <v>10</v>
@@ -16930,27 +16933,27 @@
         <v>74021</v>
       </c>
       <c r="I499" s="1" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A500" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B500" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B500" s="3" t="s">
-        <v>588</v>
-      </c>
       <c r="C500" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D500" t="s">
-        <v>11</v>
+        <v>518</v>
       </c>
       <c r="E500" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="F500" t="s">
-        <v>537</v>
+        <v>10</v>
       </c>
       <c r="G500" t="s">
         <v>11</v>
@@ -16959,27 +16962,27 @@
         <v>74021</v>
       </c>
       <c r="I500" s="1" t="s">
-        <v>253</v>
+        <v>72</v>
       </c>
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A501" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="B501" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C501" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D501" t="s">
+        <v>11</v>
+      </c>
+      <c r="E501" t="s">
         <v>590</v>
       </c>
-      <c r="B501" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C501" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D501" t="s">
-        <v>517</v>
-      </c>
-      <c r="E501" t="s">
-        <v>589</v>
-      </c>
       <c r="F501" t="s">
-        <v>10</v>
+        <v>538</v>
       </c>
       <c r="G501" t="s">
         <v>11</v>
@@ -16988,7 +16991,7 @@
         <v>74021</v>
       </c>
       <c r="I501" s="1" t="s">
-        <v>31</v>
+        <v>253</v>
       </c>
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.35">
@@ -16996,16 +16999,16 @@
         <v>591</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>592</v>
+        <v>47</v>
       </c>
       <c r="C502" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D502" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E502" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F502" t="s">
         <v>10</v>
@@ -17017,24 +17020,24 @@
         <v>74021</v>
       </c>
       <c r="I502" s="1" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A503" s="3" t="s">
-        <v>17</v>
+        <v>592</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>25</v>
+        <v>593</v>
       </c>
       <c r="C503" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D503" t="s">
-        <v>228</v>
+        <v>518</v>
       </c>
       <c r="E503" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F503" t="s">
         <v>10</v>
@@ -17046,15 +17049,15 @@
         <v>74021</v>
       </c>
       <c r="I503" s="1" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A504" s="3" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="B504" s="3" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C504" s="1" t="s">
         <v>7</v>
@@ -17063,7 +17066,7 @@
         <v>228</v>
       </c>
       <c r="E504" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F504" t="s">
         <v>10</v>
@@ -17075,24 +17078,24 @@
         <v>74021</v>
       </c>
       <c r="I504" s="1" t="s">
-        <v>345</v>
+        <v>12</v>
       </c>
     </row>
     <row r="505" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A505" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="C505" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D505" t="s">
-        <v>517</v>
+        <v>228</v>
       </c>
       <c r="E505" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F505" t="s">
         <v>10</v>
@@ -17104,24 +17107,24 @@
         <v>74021</v>
       </c>
       <c r="I505" s="1" t="s">
-        <v>12</v>
+        <v>345</v>
       </c>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A506" s="3" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>578</v>
+        <v>6</v>
       </c>
       <c r="C506" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D506" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E506" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F506" t="s">
         <v>10</v>
@@ -17133,25 +17136,25 @@
         <v>74021</v>
       </c>
       <c r="I506" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="507" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A507" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B507" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D507" t="s">
+        <v>518</v>
+      </c>
+      <c r="E507" t="s">
         <v>594</v>
       </c>
-      <c r="B507" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="C507" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D507" t="s">
-        <v>517</v>
-      </c>
-      <c r="E507" t="s">
-        <v>593</v>
-      </c>
       <c r="F507" t="s">
         <v>10</v>
       </c>
@@ -17162,27 +17165,27 @@
         <v>74021</v>
       </c>
       <c r="I507" s="1" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="508" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A508" s="3" t="s">
-        <v>131</v>
+        <v>595</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>207</v>
+        <v>596</v>
       </c>
       <c r="C508" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D508" t="s">
-        <v>14</v>
+        <v>518</v>
       </c>
       <c r="E508" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F508" t="s">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="G508" t="s">
         <v>11</v>
@@ -17191,27 +17194,27 @@
         <v>74021</v>
       </c>
       <c r="I508" s="1" t="s">
-        <v>253</v>
+        <v>72</v>
       </c>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A509" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B509" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D509" t="s">
+        <v>14</v>
+      </c>
+      <c r="E509" t="s">
         <v>597</v>
       </c>
-      <c r="B509" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C509" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D509" t="s">
-        <v>517</v>
-      </c>
-      <c r="E509" t="s">
-        <v>598</v>
-      </c>
       <c r="F509" t="s">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="G509" t="s">
         <v>11</v>
@@ -17220,27 +17223,27 @@
         <v>74021</v>
       </c>
       <c r="I509" s="1" t="s">
-        <v>31</v>
+        <v>253</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A510" s="3" t="s">
-        <v>219</v>
+        <v>598</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>227</v>
+        <v>47</v>
       </c>
       <c r="C510" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D510" t="s">
-        <v>11</v>
+        <v>518</v>
       </c>
       <c r="E510" t="s">
         <v>599</v>
       </c>
       <c r="F510" t="s">
-        <v>537</v>
+        <v>10</v>
       </c>
       <c r="G510" t="s">
         <v>11</v>
@@ -17249,27 +17252,27 @@
         <v>74021</v>
       </c>
       <c r="I510" s="1" t="s">
-        <v>253</v>
+        <v>31</v>
       </c>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A511" s="3" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>292</v>
+        <v>227</v>
       </c>
       <c r="C511" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D511" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E511" t="s">
         <v>600</v>
       </c>
       <c r="F511" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="G511" t="s">
         <v>11</v>
@@ -17278,15 +17281,15 @@
         <v>74021</v>
       </c>
       <c r="I511" s="1" t="s">
-        <v>12</v>
+        <v>253</v>
       </c>
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A512" s="3" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>347</v>
+        <v>292</v>
       </c>
       <c r="C512" s="1" t="s">
         <v>7</v>
@@ -17295,10 +17298,10 @@
         <v>14</v>
       </c>
       <c r="E512" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F512" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G512" t="s">
         <v>11</v>
@@ -17307,27 +17310,27 @@
         <v>74021</v>
       </c>
       <c r="I512" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="513" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A513" s="3" t="s">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="B513" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D513" t="s">
+        <v>14</v>
+      </c>
+      <c r="E513" t="s">
         <v>601</v>
       </c>
-      <c r="C513" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D513" t="s">
-        <v>14</v>
-      </c>
-      <c r="E513" t="s">
-        <v>600</v>
-      </c>
       <c r="F513" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G513" t="s">
         <v>11</v>
@@ -17336,27 +17339,27 @@
         <v>74021</v>
       </c>
       <c r="I513" s="1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A514" s="3" t="s">
-        <v>181</v>
+        <v>257</v>
       </c>
       <c r="B514" s="3" t="s">
-        <v>164</v>
+        <v>602</v>
       </c>
       <c r="C514" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D514" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E514" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F514" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="G514" t="s">
         <v>11</v>
@@ -17365,15 +17368,15 @@
         <v>74021</v>
       </c>
       <c r="I514" s="1" t="s">
-        <v>253</v>
+        <v>48</v>
       </c>
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A515" s="3" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="C515" s="1" t="s">
         <v>7</v>
@@ -17385,7 +17388,7 @@
         <v>603</v>
       </c>
       <c r="F515" t="s">
-        <v>209</v>
+        <v>538</v>
       </c>
       <c r="G515" t="s">
         <v>11</v>
@@ -17399,22 +17402,22 @@
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A516" s="3" t="s">
-        <v>5</v>
+        <v>226</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>62</v>
+        <v>227</v>
       </c>
       <c r="C516" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D516" t="s">
-        <v>228</v>
+        <v>11</v>
       </c>
       <c r="E516" t="s">
         <v>604</v>
       </c>
       <c r="F516" t="s">
-        <v>94</v>
+        <v>209</v>
       </c>
       <c r="G516" t="s">
         <v>11</v>
@@ -17423,27 +17426,27 @@
         <v>74021</v>
       </c>
       <c r="I516" s="1" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
     </row>
     <row r="517" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A517" s="3" t="s">
-        <v>597</v>
+        <v>5</v>
       </c>
       <c r="B517" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D517" t="s">
+        <v>228</v>
+      </c>
+      <c r="E517" t="s">
         <v>605</v>
       </c>
-      <c r="C517" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D517" t="s">
-        <v>517</v>
-      </c>
-      <c r="E517" t="s">
-        <v>604</v>
-      </c>
       <c r="F517" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G517" t="s">
         <v>11</v>
@@ -17452,27 +17455,27 @@
         <v>74021</v>
       </c>
       <c r="I517" s="1" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
     </row>
     <row r="518" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A518" s="3" t="s">
-        <v>110</v>
+        <v>598</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>132</v>
+        <v>606</v>
       </c>
       <c r="C518" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D518" t="s">
-        <v>14</v>
+        <v>518</v>
       </c>
       <c r="E518" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F518" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G518" t="s">
         <v>11</v>
@@ -17481,15 +17484,15 @@
         <v>74021</v>
       </c>
       <c r="I518" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A519" s="3" t="s">
-        <v>222</v>
+        <v>106</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>249</v>
+        <v>131</v>
       </c>
       <c r="C519" s="1" t="s">
         <v>7</v>
@@ -17498,7 +17501,7 @@
         <v>14</v>
       </c>
       <c r="E519" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F519" t="s">
         <v>11</v>
@@ -17510,25 +17513,25 @@
         <v>74021</v>
       </c>
       <c r="I519" s="1" t="s">
-        <v>345</v>
+        <v>12</v>
       </c>
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A520" s="3" t="s">
-        <v>566</v>
+        <v>222</v>
       </c>
       <c r="B520" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D520" t="s">
+        <v>14</v>
+      </c>
+      <c r="E520" t="s">
         <v>607</v>
       </c>
-      <c r="C520" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D520" t="s">
-        <v>228</v>
-      </c>
-      <c r="E520" t="s">
-        <v>608</v>
-      </c>
       <c r="F520" t="s">
         <v>11</v>
       </c>
@@ -17539,27 +17542,27 @@
         <v>74021</v>
       </c>
       <c r="I520" s="1" t="s">
-        <v>253</v>
+        <v>345</v>
       </c>
     </row>
     <row r="521" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A521" s="3" t="s">
-        <v>157</v>
+        <v>567</v>
       </c>
       <c r="B521" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C521" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D521" t="s">
+        <v>228</v>
+      </c>
+      <c r="E521" t="s">
         <v>609</v>
       </c>
-      <c r="C521" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D521" t="s">
-        <v>11</v>
-      </c>
-      <c r="E521" t="s">
-        <v>610</v>
-      </c>
       <c r="F521" t="s">
-        <v>611</v>
+        <v>11</v>
       </c>
       <c r="G521" t="s">
         <v>11</v>
@@ -17576,19 +17579,19 @@
         <v>157</v>
       </c>
       <c r="B522" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D522" t="s">
+        <v>11</v>
+      </c>
+      <c r="E522" t="s">
+        <v>611</v>
+      </c>
+      <c r="F522" t="s">
         <v>612</v>
-      </c>
-      <c r="C522" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D522" t="s">
-        <v>11</v>
-      </c>
-      <c r="E522" t="s">
-        <v>613</v>
-      </c>
-      <c r="F522" t="s">
-        <v>537</v>
       </c>
       <c r="G522" t="s">
         <v>11</v>
@@ -17602,22 +17605,22 @@
     </row>
     <row r="523" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A523" s="3" t="s">
-        <v>567</v>
+        <v>157</v>
       </c>
       <c r="B523" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D523" t="s">
+        <v>11</v>
+      </c>
+      <c r="E523" t="s">
         <v>614</v>
       </c>
-      <c r="C523" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D523" t="s">
-        <v>11</v>
-      </c>
-      <c r="E523" t="s">
-        <v>613</v>
-      </c>
       <c r="F523" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="G523" t="s">
         <v>11</v>
@@ -17631,22 +17634,22 @@
     </row>
     <row r="524" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A524" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B524" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="B524" s="3" t="s">
-        <v>609</v>
-      </c>
       <c r="C524" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D524" t="s">
-        <v>228</v>
+        <v>11</v>
       </c>
       <c r="E524" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F524" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G524" t="s">
         <v>11</v>
@@ -17660,10 +17663,10 @@
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A525" s="3" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="C525" s="1" t="s">
         <v>7</v>
@@ -17672,10 +17675,10 @@
         <v>228</v>
       </c>
       <c r="E525" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F525" t="s">
-        <v>617</v>
+        <v>520</v>
       </c>
       <c r="G525" t="s">
         <v>11</v>
@@ -17689,23 +17692,23 @@
     </row>
     <row r="526" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A526" s="3" t="s">
-        <v>296</v>
+        <v>588</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>107</v>
+        <v>617</v>
       </c>
       <c r="C526" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D526" t="s">
-        <v>11</v>
+        <v>228</v>
       </c>
       <c r="E526" t="s">
+        <v>614</v>
+      </c>
+      <c r="F526" t="s">
         <v>618</v>
       </c>
-      <c r="F526" t="s">
-        <v>619</v>
-      </c>
       <c r="G526" t="s">
         <v>11</v>
       </c>
@@ -17713,15 +17716,15 @@
         <v>74021</v>
       </c>
       <c r="I526" s="1" t="s">
-        <v>345</v>
+        <v>253</v>
       </c>
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A527" s="3" t="s">
-        <v>142</v>
+        <v>296</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C527" s="1" t="s">
         <v>7</v>
@@ -17730,11 +17733,11 @@
         <v>11</v>
       </c>
       <c r="E527" t="s">
+        <v>619</v>
+      </c>
+      <c r="F527" t="s">
         <v>620</v>
       </c>
-      <c r="F527" t="s">
-        <v>94</v>
-      </c>
       <c r="G527" t="s">
         <v>11</v>
       </c>
@@ -17742,27 +17745,27 @@
         <v>74021</v>
       </c>
       <c r="I527" s="1" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
     </row>
     <row r="528" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A528" s="3" t="s">
-        <v>293</v>
+        <v>141</v>
       </c>
       <c r="B528" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D528" t="s">
+        <v>11</v>
+      </c>
+      <c r="E528" t="s">
         <v>621</v>
       </c>
-      <c r="C528" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D528" t="s">
-        <v>11</v>
-      </c>
-      <c r="E528" t="s">
-        <v>622</v>
-      </c>
       <c r="F528" t="s">
-        <v>519</v>
+        <v>94</v>
       </c>
       <c r="G528" t="s">
         <v>11</v>
@@ -17771,27 +17774,27 @@
         <v>74021</v>
       </c>
       <c r="I528" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A529" s="3" t="s">
-        <v>17</v>
+        <v>293</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>32</v>
+        <v>622</v>
       </c>
       <c r="C529" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D529" t="s">
-        <v>228</v>
+        <v>11</v>
       </c>
       <c r="E529" t="s">
         <v>623</v>
       </c>
       <c r="F529" t="s">
-        <v>10</v>
+        <v>520</v>
       </c>
       <c r="G529" t="s">
         <v>11</v>
@@ -17800,15 +17803,15 @@
         <v>74021</v>
       </c>
       <c r="I529" s="1" t="s">
-        <v>12</v>
+        <v>253</v>
       </c>
     </row>
     <row r="530" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A530" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C530" s="1" t="s">
         <v>7</v>
@@ -17817,7 +17820,7 @@
         <v>228</v>
       </c>
       <c r="E530" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F530" t="s">
         <v>10</v>
@@ -17829,15 +17832,15 @@
         <v>74021</v>
       </c>
       <c r="I530" s="1" t="s">
-        <v>253</v>
+        <v>12</v>
       </c>
     </row>
     <row r="531" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A531" s="3" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="C531" s="1" t="s">
         <v>7</v>
@@ -17846,7 +17849,7 @@
         <v>228</v>
       </c>
       <c r="E531" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F531" t="s">
         <v>10</v>
@@ -17858,24 +17861,24 @@
         <v>74021</v>
       </c>
       <c r="I531" s="1" t="s">
-        <v>345</v>
+        <v>253</v>
       </c>
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A532" s="3" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="B532" s="3" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C532" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D532" t="s">
-        <v>517</v>
+        <v>228</v>
       </c>
       <c r="E532" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F532" t="s">
         <v>10</v>
@@ -17887,24 +17890,24 @@
         <v>74021</v>
       </c>
       <c r="I532" s="1" t="s">
-        <v>12</v>
+        <v>345</v>
       </c>
     </row>
     <row r="533" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A533" s="3" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>578</v>
+        <v>25</v>
       </c>
       <c r="C533" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D533" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E533" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F533" t="s">
         <v>10</v>
@@ -17916,24 +17919,24 @@
         <v>74021</v>
       </c>
       <c r="I533" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="534" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A534" s="3" t="s">
-        <v>591</v>
+        <v>29</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C534" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D534" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E534" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F534" t="s">
         <v>10</v>
@@ -17945,27 +17948,27 @@
         <v>74021</v>
       </c>
       <c r="I534" s="1" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="535" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A535" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="B535" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C535" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D535" t="s">
+        <v>518</v>
+      </c>
+      <c r="E535" t="s">
         <v>624</v>
       </c>
-      <c r="B535" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="C535" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D535" t="s">
-        <v>228</v>
-      </c>
-      <c r="E535" t="s">
-        <v>626</v>
-      </c>
       <c r="F535" t="s">
-        <v>537</v>
+        <v>10</v>
       </c>
       <c r="G535" t="s">
         <v>11</v>
@@ -17974,27 +17977,27 @@
         <v>74021</v>
       </c>
       <c r="I535" s="1" t="s">
-        <v>253</v>
+        <v>72</v>
       </c>
     </row>
     <row r="536" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A536" s="3" t="s">
-        <v>115</v>
+        <v>625</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>92</v>
+        <v>626</v>
       </c>
       <c r="C536" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D536" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E536" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F536" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="G536" t="s">
         <v>11</v>
@@ -18003,27 +18006,27 @@
         <v>74021</v>
       </c>
       <c r="I536" s="1" t="s">
-        <v>345</v>
+        <v>253</v>
       </c>
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A537" s="3" t="s">
-        <v>585</v>
+        <v>114</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>586</v>
+        <v>92</v>
       </c>
       <c r="C537" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D537" t="s">
-        <v>517</v>
+        <v>14</v>
       </c>
       <c r="E537" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F537" t="s">
-        <v>64</v>
+        <v>520</v>
       </c>
       <c r="G537" t="s">
         <v>11</v>
@@ -18032,27 +18035,27 @@
         <v>74021</v>
       </c>
       <c r="I537" s="1" t="s">
-        <v>31</v>
+        <v>345</v>
       </c>
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A538" s="3" t="s">
-        <v>77</v>
+        <v>586</v>
       </c>
       <c r="B538" s="3" t="s">
-        <v>51</v>
+        <v>587</v>
       </c>
       <c r="C538" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D538" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E538" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F538" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G538" t="s">
         <v>11</v>
@@ -18061,24 +18064,24 @@
         <v>74021</v>
       </c>
       <c r="I538" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="539" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A539" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>586</v>
+        <v>51</v>
       </c>
       <c r="C539" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D539" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E539" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F539" t="s">
         <v>10</v>
@@ -18090,25 +18093,25 @@
         <v>74021</v>
       </c>
       <c r="I539" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A540" s="3" t="s">
-        <v>574</v>
+        <v>71</v>
       </c>
       <c r="B540" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D540" t="s">
+        <v>518</v>
+      </c>
+      <c r="E540" t="s">
         <v>627</v>
       </c>
-      <c r="C540" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D540" t="s">
-        <v>517</v>
-      </c>
-      <c r="E540" t="s">
-        <v>626</v>
-      </c>
       <c r="F540" t="s">
         <v>10</v>
       </c>
@@ -18119,27 +18122,27 @@
         <v>74021</v>
       </c>
       <c r="I540" s="1" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A541" s="3" t="s">
-        <v>226</v>
+        <v>575</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>216</v>
+        <v>628</v>
       </c>
       <c r="C541" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D541" t="s">
-        <v>14</v>
+        <v>518</v>
       </c>
       <c r="E541" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F541" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G541" t="s">
         <v>11</v>
@@ -18148,27 +18151,27 @@
         <v>74021</v>
       </c>
       <c r="I541" s="1" t="s">
-        <v>250</v>
+        <v>59</v>
       </c>
     </row>
     <row r="542" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A542" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B542" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D542" t="s">
+        <v>14</v>
+      </c>
+      <c r="E542" t="s">
         <v>629</v>
       </c>
-      <c r="B542" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C542" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D542" t="s">
-        <v>14</v>
-      </c>
-      <c r="E542" t="s">
-        <v>630</v>
-      </c>
       <c r="F542" t="s">
-        <v>537</v>
+        <v>94</v>
       </c>
       <c r="G542" t="s">
         <v>11</v>
@@ -18177,27 +18180,27 @@
         <v>74021</v>
       </c>
       <c r="I542" s="1" t="s">
-        <v>105</v>
+        <v>250</v>
       </c>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A543" s="3" t="s">
-        <v>96</v>
+        <v>630</v>
       </c>
       <c r="B543" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D543" t="s">
+        <v>14</v>
+      </c>
+      <c r="E543" t="s">
         <v>631</v>
       </c>
-      <c r="C543" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D543" t="s">
-        <v>14</v>
-      </c>
-      <c r="E543" t="s">
-        <v>630</v>
-      </c>
       <c r="F543" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G543" t="s">
         <v>11</v>
@@ -18206,16 +18209,16 @@
         <v>74021</v>
       </c>
       <c r="I543" s="1" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A544" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B544" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="B544" s="3" t="s">
-        <v>633</v>
-      </c>
       <c r="C544" s="1" t="s">
         <v>7</v>
       </c>
@@ -18223,10 +18226,10 @@
         <v>14</v>
       </c>
       <c r="E544" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F544" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G544" t="s">
         <v>11</v>
@@ -18235,15 +18238,15 @@
         <v>74021</v>
       </c>
       <c r="I544" s="1" t="s">
-        <v>176</v>
+        <v>59</v>
       </c>
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A545" s="3" t="s">
-        <v>142</v>
+        <v>633</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>161</v>
+        <v>634</v>
       </c>
       <c r="C545" s="1" t="s">
         <v>7</v>
@@ -18252,10 +18255,10 @@
         <v>14</v>
       </c>
       <c r="E545" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F545" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="G545" t="s">
         <v>11</v>
@@ -18264,27 +18267,27 @@
         <v>74021</v>
       </c>
       <c r="I545" s="1" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
     </row>
     <row r="546" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A546" s="3" t="s">
-        <v>230</v>
+        <v>141</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="C546" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D546" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E546" t="s">
         <v>635</v>
       </c>
       <c r="F546" t="s">
-        <v>94</v>
+        <v>520</v>
       </c>
       <c r="G546" t="s">
         <v>11</v>
@@ -18293,27 +18296,27 @@
         <v>74021</v>
       </c>
       <c r="I546" s="1" t="s">
-        <v>253</v>
+        <v>59</v>
       </c>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A547" s="3" t="s">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="B547" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C547" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D547" t="s">
+        <v>11</v>
+      </c>
+      <c r="E547" t="s">
         <v>636</v>
       </c>
-      <c r="C547" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D547" t="s">
-        <v>517</v>
-      </c>
-      <c r="E547" t="s">
-        <v>637</v>
-      </c>
       <c r="F547" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G547" t="s">
         <v>11</v>
@@ -18322,24 +18325,24 @@
         <v>74021</v>
       </c>
       <c r="I547" s="1" t="s">
-        <v>16</v>
+        <v>253</v>
       </c>
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A548" s="3" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>586</v>
+        <v>637</v>
       </c>
       <c r="C548" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D548" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E548" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F548" t="s">
         <v>10</v>
@@ -18351,27 +18354,27 @@
         <v>74021</v>
       </c>
       <c r="I548" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A549" s="3" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>347</v>
+        <v>587</v>
       </c>
       <c r="C549" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D549" t="s">
-        <v>14</v>
+        <v>518</v>
       </c>
       <c r="E549" t="s">
         <v>638</v>
       </c>
       <c r="F549" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G549" t="s">
         <v>11</v>
@@ -18380,85 +18383,85 @@
         <v>74021</v>
       </c>
       <c r="I549" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A550" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B550" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C550" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D550" t="s">
+        <v>14</v>
+      </c>
+      <c r="E550" t="s">
         <v>639</v>
       </c>
-      <c r="B550" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="C550" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D550" t="s">
-        <v>228</v>
-      </c>
-      <c r="E550" t="s">
-        <v>641</v>
-      </c>
       <c r="F550" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G550" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H550">
         <v>74021</v>
       </c>
       <c r="I550" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="551" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A551" s="3" t="s">
-        <v>46</v>
+        <v>640</v>
       </c>
       <c r="B551" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C551" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D551" t="s">
+        <v>228</v>
+      </c>
+      <c r="E551" t="s">
         <v>642</v>
       </c>
-      <c r="C551" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D551" t="s">
-        <v>517</v>
-      </c>
-      <c r="E551" t="s">
-        <v>643</v>
-      </c>
       <c r="F551" t="s">
         <v>10</v>
       </c>
       <c r="G551" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H551">
         <v>74021</v>
       </c>
       <c r="I551" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="552" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A552" s="3" t="s">
-        <v>293</v>
+        <v>46</v>
       </c>
       <c r="B552" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C552" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D552" t="s">
+        <v>518</v>
+      </c>
+      <c r="E552" t="s">
         <v>644</v>
       </c>
-      <c r="C552" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D552" t="s">
-        <v>11</v>
-      </c>
-      <c r="E552" t="s">
-        <v>645</v>
-      </c>
       <c r="F552" t="s">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="G552" t="s">
         <v>11</v>
@@ -18467,27 +18470,27 @@
         <v>74021</v>
       </c>
       <c r="I552" s="1" t="s">
-        <v>253</v>
+        <v>31</v>
       </c>
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A553" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B553" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C553" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D553" t="s">
+        <v>11</v>
+      </c>
+      <c r="E553" t="s">
         <v>646</v>
       </c>
-      <c r="B553" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="C553" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D553" t="s">
-        <v>517</v>
-      </c>
-      <c r="E553" t="s">
-        <v>647</v>
-      </c>
       <c r="F553" t="s">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="G553" t="s">
         <v>11</v>
@@ -18496,27 +18499,27 @@
         <v>74021</v>
       </c>
       <c r="I553" s="1" t="s">
-        <v>72</v>
+        <v>253</v>
       </c>
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A554" s="3" t="s">
-        <v>206</v>
+        <v>647</v>
       </c>
       <c r="B554" s="3" t="s">
-        <v>200</v>
+        <v>587</v>
       </c>
       <c r="C554" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D554" t="s">
-        <v>11</v>
+        <v>518</v>
       </c>
       <c r="E554" t="s">
         <v>648</v>
       </c>
       <c r="F554" t="s">
-        <v>569</v>
+        <v>10</v>
       </c>
       <c r="G554" t="s">
         <v>11</v>
@@ -18525,27 +18528,27 @@
         <v>74021</v>
       </c>
       <c r="I554" s="1" t="s">
-        <v>253</v>
+        <v>72</v>
       </c>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A555" s="3" t="s">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>584</v>
+        <v>200</v>
       </c>
       <c r="C555" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D555" t="s">
-        <v>517</v>
+        <v>11</v>
       </c>
       <c r="E555" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F555" t="s">
-        <v>10</v>
+        <v>570</v>
       </c>
       <c r="G555" t="s">
         <v>11</v>
@@ -18554,25 +18557,25 @@
         <v>74021</v>
       </c>
       <c r="I555" s="1" t="s">
-        <v>16</v>
+        <v>253</v>
       </c>
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A556" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B556" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C556" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D556" t="s">
+        <v>518</v>
+      </c>
+      <c r="E556" t="s">
         <v>649</v>
       </c>
-      <c r="B556" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="C556" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D556" t="s">
-        <v>517</v>
-      </c>
-      <c r="E556" t="s">
-        <v>648</v>
-      </c>
       <c r="F556" t="s">
         <v>10</v>
       </c>
@@ -18583,27 +18586,27 @@
         <v>74021</v>
       </c>
       <c r="I556" s="1" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A557" s="3" t="s">
-        <v>29</v>
+        <v>650</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>26</v>
+        <v>651</v>
       </c>
       <c r="C557" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D557" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E557" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F557" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G557" t="s">
         <v>11</v>
@@ -18612,27 +18615,27 @@
         <v>74021</v>
       </c>
       <c r="I557" s="1" t="s">
-        <v>176</v>
+        <v>72</v>
       </c>
     </row>
     <row r="558" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A558" s="3" t="s">
-        <v>174</v>
+        <v>29</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>644</v>
+        <v>26</v>
       </c>
       <c r="C558" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D558" t="s">
-        <v>11</v>
+        <v>518</v>
       </c>
       <c r="E558" t="s">
         <v>652</v>
       </c>
       <c r="F558" t="s">
-        <v>519</v>
+        <v>94</v>
       </c>
       <c r="G558" t="s">
         <v>11</v>
@@ -18641,15 +18644,15 @@
         <v>74021</v>
       </c>
       <c r="I558" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A559" s="3" t="s">
-        <v>293</v>
+        <v>174</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="C559" s="1" t="s">
         <v>7</v>
@@ -18661,7 +18664,7 @@
         <v>653</v>
       </c>
       <c r="F559" t="s">
-        <v>569</v>
+        <v>520</v>
       </c>
       <c r="G559" t="s">
         <v>11</v>
@@ -18675,10 +18678,10 @@
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A560" s="3" t="s">
-        <v>181</v>
+        <v>293</v>
       </c>
       <c r="B560" s="3" t="s">
-        <v>196</v>
+        <v>622</v>
       </c>
       <c r="C560" s="1" t="s">
         <v>7</v>
@@ -18690,7 +18693,7 @@
         <v>654</v>
       </c>
       <c r="F560" t="s">
-        <v>209</v>
+        <v>570</v>
       </c>
       <c r="G560" t="s">
         <v>11</v>
@@ -18704,22 +18707,22 @@
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A561" s="3" t="s">
-        <v>646</v>
+        <v>181</v>
       </c>
       <c r="B561" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C561" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D561" t="s">
+        <v>11</v>
+      </c>
+      <c r="E561" t="s">
         <v>655</v>
       </c>
-      <c r="C561" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D561" t="s">
-        <v>517</v>
-      </c>
-      <c r="E561" t="s">
-        <v>656</v>
-      </c>
       <c r="F561" t="s">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="G561" t="s">
         <v>11</v>
@@ -18728,27 +18731,27 @@
         <v>74021</v>
       </c>
       <c r="I561" s="1" t="s">
-        <v>72</v>
+        <v>253</v>
       </c>
     </row>
     <row r="562" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A562" s="3" t="s">
-        <v>215</v>
+        <v>647</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>216</v>
+        <v>656</v>
       </c>
       <c r="C562" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D562" t="s">
-        <v>11</v>
+        <v>518</v>
       </c>
       <c r="E562" t="s">
         <v>657</v>
       </c>
       <c r="F562" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G562" t="s">
         <v>11</v>
@@ -18757,15 +18760,15 @@
         <v>74021</v>
       </c>
       <c r="I562" s="1" t="s">
-        <v>253</v>
+        <v>72</v>
       </c>
     </row>
     <row r="563" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A563" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="C563" s="1" t="s">
         <v>7</v>
@@ -18777,7 +18780,7 @@
         <v>658</v>
       </c>
       <c r="F563" t="s">
-        <v>537</v>
+        <v>94</v>
       </c>
       <c r="G563" t="s">
         <v>11</v>
@@ -18791,22 +18794,22 @@
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A564" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C564" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D564" t="s">
+        <v>11</v>
+      </c>
+      <c r="E564" t="s">
         <v>659</v>
       </c>
-      <c r="B564" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="C564" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D564" t="s">
-        <v>11</v>
-      </c>
-      <c r="E564" t="s">
-        <v>661</v>
-      </c>
       <c r="F564" t="s">
-        <v>209</v>
+        <v>538</v>
       </c>
       <c r="G564" t="s">
         <v>11</v>
@@ -18820,22 +18823,22 @@
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A565" s="3" t="s">
-        <v>233</v>
+        <v>660</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>318</v>
+        <v>661</v>
       </c>
       <c r="C565" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D565" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E565" t="s">
         <v>662</v>
       </c>
       <c r="F565" t="s">
-        <v>519</v>
+        <v>209</v>
       </c>
       <c r="G565" t="s">
         <v>11</v>
@@ -18844,15 +18847,15 @@
         <v>74021</v>
       </c>
       <c r="I565" s="1" t="s">
-        <v>105</v>
+        <v>253</v>
       </c>
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A566" s="3" t="s">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="B566" s="3" t="s">
-        <v>92</v>
+        <v>318</v>
       </c>
       <c r="C566" s="1" t="s">
         <v>7</v>
@@ -18861,10 +18864,10 @@
         <v>14</v>
       </c>
       <c r="E566" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F566" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G566" t="s">
         <v>11</v>
@@ -18873,27 +18876,27 @@
         <v>74021</v>
       </c>
       <c r="I566" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A567" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C567" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D567" t="s">
+        <v>14</v>
+      </c>
+      <c r="E567" t="s">
         <v>663</v>
       </c>
-      <c r="B567" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="C567" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D567" t="s">
-        <v>14</v>
-      </c>
-      <c r="E567" t="s">
-        <v>662</v>
-      </c>
       <c r="F567" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G567" t="s">
         <v>11</v>
@@ -18902,27 +18905,27 @@
         <v>74021</v>
       </c>
       <c r="I567" s="1" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A568" s="3" t="s">
-        <v>226</v>
+        <v>664</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>207</v>
+        <v>665</v>
       </c>
       <c r="C568" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D568" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E568" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F568" t="s">
-        <v>569</v>
+        <v>520</v>
       </c>
       <c r="G568" t="s">
         <v>11</v>
@@ -18931,27 +18934,27 @@
         <v>74021</v>
       </c>
       <c r="I568" s="1" t="s">
-        <v>253</v>
+        <v>59</v>
       </c>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A569" s="3" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="B569" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C569" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D569" t="s">
+        <v>11</v>
+      </c>
+      <c r="E569" t="s">
         <v>666</v>
       </c>
-      <c r="C569" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D569" t="s">
-        <v>11</v>
-      </c>
-      <c r="E569" t="s">
-        <v>665</v>
-      </c>
       <c r="F569" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="G569" t="s">
         <v>11</v>
@@ -18965,22 +18968,22 @@
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A570" s="3" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="B570" s="3" t="s">
-        <v>627</v>
+        <v>667</v>
       </c>
       <c r="C570" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D570" t="s">
-        <v>517</v>
+        <v>11</v>
       </c>
       <c r="E570" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F570" t="s">
-        <v>10</v>
+        <v>538</v>
       </c>
       <c r="G570" t="s">
         <v>11</v>
@@ -18989,24 +18992,24 @@
         <v>74021</v>
       </c>
       <c r="I570" s="1" t="s">
-        <v>16</v>
+        <v>253</v>
       </c>
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A571" s="3" t="s">
-        <v>591</v>
+        <v>58</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="C571" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D571" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E571" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F571" t="s">
         <v>10</v>
@@ -19018,21 +19021,21 @@
         <v>74021</v>
       </c>
       <c r="I571" s="1" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A572" s="3" t="s">
-        <v>77</v>
+        <v>592</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>34</v>
+        <v>582</v>
       </c>
       <c r="C572" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D572" t="s">
-        <v>228</v>
+        <v>518</v>
       </c>
       <c r="E572" t="s">
         <v>668</v>
@@ -19047,25 +19050,25 @@
         <v>74021</v>
       </c>
       <c r="I572" s="1" t="s">
-        <v>345</v>
+        <v>72</v>
       </c>
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A573" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B573" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D573" t="s">
+        <v>228</v>
+      </c>
+      <c r="E573" t="s">
         <v>669</v>
       </c>
-      <c r="C573" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D573" t="s">
-        <v>517</v>
-      </c>
-      <c r="E573" t="s">
-        <v>668</v>
-      </c>
       <c r="F573" t="s">
         <v>10</v>
       </c>
@@ -19076,12 +19079,12 @@
         <v>74021</v>
       </c>
       <c r="I573" s="1" t="s">
-        <v>16</v>
+        <v>345</v>
       </c>
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A574" s="3" t="s">
-        <v>597</v>
+        <v>66</v>
       </c>
       <c r="B574" s="3" t="s">
         <v>670</v>
@@ -19090,10 +19093,10 @@
         <v>7</v>
       </c>
       <c r="D574" t="s">
-        <v>11</v>
+        <v>518</v>
       </c>
       <c r="E574" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F574" t="s">
         <v>10</v>
@@ -19105,27 +19108,27 @@
         <v>74021</v>
       </c>
       <c r="I574" s="1" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A575" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B575" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D575" t="s">
+        <v>11</v>
+      </c>
+      <c r="E575" t="s">
         <v>672</v>
       </c>
-      <c r="B575" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="C575" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D575" t="s">
-        <v>517</v>
-      </c>
-      <c r="E575" t="s">
-        <v>673</v>
-      </c>
       <c r="F575" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G575" t="s">
         <v>11</v>
@@ -19134,27 +19137,27 @@
         <v>74021</v>
       </c>
       <c r="I575" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="576" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A576" s="3" t="s">
-        <v>85</v>
+        <v>673</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>89</v>
+        <v>576</v>
       </c>
       <c r="C576" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D576" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E576" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F576" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G576" t="s">
         <v>11</v>
@@ -19163,25 +19166,25 @@
         <v>74021</v>
       </c>
       <c r="I576" s="1" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A577" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B577" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C577" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D577" t="s">
+        <v>518</v>
+      </c>
+      <c r="E577" t="s">
         <v>674</v>
       </c>
-      <c r="B577" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="C577" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D577" t="s">
-        <v>517</v>
-      </c>
-      <c r="E577" t="s">
-        <v>673</v>
-      </c>
       <c r="F577" t="s">
         <v>10</v>
       </c>
@@ -19192,27 +19195,27 @@
         <v>74021</v>
       </c>
       <c r="I577" s="1" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A578" s="3" t="s">
-        <v>181</v>
+        <v>675</v>
       </c>
       <c r="B578" s="3" t="s">
-        <v>660</v>
+        <v>576</v>
       </c>
       <c r="C578" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D578" t="s">
-        <v>11</v>
+        <v>518</v>
       </c>
       <c r="E578" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F578" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G578" t="s">
         <v>11</v>
@@ -19221,27 +19224,27 @@
         <v>74021</v>
       </c>
       <c r="I578" s="1" t="s">
-        <v>253</v>
+        <v>59</v>
       </c>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A579" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C579" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D579" t="s">
+        <v>11</v>
+      </c>
+      <c r="E579" t="s">
         <v>676</v>
       </c>
-      <c r="B579" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="C579" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D579" t="s">
-        <v>8</v>
-      </c>
-      <c r="E579" t="s">
-        <v>678</v>
-      </c>
       <c r="F579" t="s">
-        <v>209</v>
+        <v>94</v>
       </c>
       <c r="G579" t="s">
         <v>11</v>
@@ -19255,22 +19258,22 @@
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A580" s="3" t="s">
-        <v>77</v>
+        <v>677</v>
       </c>
       <c r="B580" s="3" t="s">
-        <v>76</v>
+        <v>678</v>
       </c>
       <c r="C580" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D580" t="s">
-        <v>517</v>
+        <v>8</v>
       </c>
       <c r="E580" t="s">
         <v>679</v>
       </c>
       <c r="F580" t="s">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="G580" t="s">
         <v>11</v>
@@ -19279,24 +19282,24 @@
         <v>74021</v>
       </c>
       <c r="I580" s="1" t="s">
-        <v>16</v>
+        <v>253</v>
       </c>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A581" s="3" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>586</v>
+        <v>76</v>
       </c>
       <c r="C581" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D581" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E581" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F581" t="s">
         <v>10</v>
@@ -19308,27 +19311,27 @@
         <v>74021</v>
       </c>
       <c r="I581" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A582" s="3" t="s">
-        <v>206</v>
+        <v>58</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>200</v>
+        <v>587</v>
       </c>
       <c r="C582" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D582" t="s">
-        <v>14</v>
+        <v>518</v>
       </c>
       <c r="E582" t="s">
         <v>680</v>
       </c>
       <c r="F582" t="s">
-        <v>569</v>
+        <v>10</v>
       </c>
       <c r="G582" t="s">
         <v>11</v>
@@ -19337,27 +19340,27 @@
         <v>74021</v>
       </c>
       <c r="I582" s="1" t="s">
-        <v>253</v>
+        <v>31</v>
       </c>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A583" s="3" t="s">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="B583" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C583" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D583" t="s">
+        <v>14</v>
+      </c>
+      <c r="E583" t="s">
         <v>681</v>
       </c>
-      <c r="C583" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D583" t="s">
-        <v>228</v>
-      </c>
-      <c r="E583" t="s">
-        <v>682</v>
-      </c>
       <c r="F583" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="G583" t="s">
         <v>11</v>
@@ -19366,27 +19369,27 @@
         <v>74021</v>
       </c>
       <c r="I583" s="1" t="s">
-        <v>345</v>
+        <v>253</v>
       </c>
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A584" s="3" t="s">
-        <v>145</v>
+        <v>257</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>277</v>
+        <v>682</v>
       </c>
       <c r="C584" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D584" t="s">
-        <v>11</v>
+        <v>228</v>
       </c>
       <c r="E584" t="s">
         <v>683</v>
       </c>
       <c r="F584" t="s">
-        <v>569</v>
+        <v>538</v>
       </c>
       <c r="G584" t="s">
         <v>11</v>
@@ -19400,52 +19403,81 @@
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A585" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B585" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D585" t="s">
+        <v>11</v>
+      </c>
+      <c r="E585" t="s">
         <v>684</v>
       </c>
-      <c r="B585" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C585" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D585" t="s">
-        <v>14</v>
-      </c>
-      <c r="E585" t="s">
+      <c r="F585" t="s">
+        <v>570</v>
+      </c>
+      <c r="G585" t="s">
+        <v>11</v>
+      </c>
+      <c r="H585">
+        <v>74021</v>
+      </c>
+      <c r="I585" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="586" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A586" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="F585" t="s">
+      <c r="B586" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D586" t="s">
+        <v>14</v>
+      </c>
+      <c r="E586" t="s">
+        <v>686</v>
+      </c>
+      <c r="F586" t="s">
         <v>94</v>
       </c>
-      <c r="G585" t="s">
-        <v>11</v>
-      </c>
-      <c r="H585">
-        <v>74021</v>
-      </c>
-      <c r="I585" s="1" t="s">
+      <c r="G586" t="s">
+        <v>11</v>
+      </c>
+      <c r="H586">
+        <v>74021</v>
+      </c>
+      <c r="I586" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A586" s="6" t="s">
-        <v>686</v>
-      </c>
-      <c r="B586" s="6"/>
-      <c r="C586" s="6"/>
-      <c r="D586" t="s">
-        <v>11</v>
-      </c>
-      <c r="E586" t="s">
-        <v>11</v>
-      </c>
-      <c r="F586" t="s">
-        <v>11</v>
-      </c>
-      <c r="G586" t="s">
-        <v>11</v>
-      </c>
-      <c r="H586" t="s">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A587" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="B587" s="6"/>
+      <c r="C587" s="6"/>
+      <c r="D587" t="s">
+        <v>11</v>
+      </c>
+      <c r="E587" t="s">
+        <v>11</v>
+      </c>
+      <c r="F587" t="s">
+        <v>11</v>
+      </c>
+      <c r="G587" t="s">
+        <v>11</v>
+      </c>
+      <c r="H587" t="s">
         <v>11</v>
       </c>
     </row>
@@ -19454,7 +19486,7 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A586:C586"/>
+    <mergeCell ref="A587:C587"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
